--- a/macro_sam_2008_analisis.xlsx
+++ b/macro_sam_2008_analisis.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\francisco.henriquez\Mis documentos\proyectos\equilibrio_general\eq_general\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF307187-9196-4FAD-95DC-7A6E6674C675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11310"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId1"/>
@@ -18,7 +19,20 @@
     <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId4"/>
     <sheet name="macro_sam_2008" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -613,10 +627,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1121,11 +1136,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1172,24 +1187,7 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill>
@@ -1205,9 +1203,12 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1243,47 +1244,12 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1360,6 +1326,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1645,7 +1632,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -1737,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="5">
-        <f>+SUM(B2:M2)</f>
+        <f t="shared" ref="N2:N13" si="0">+SUM(B2:M2)</f>
         <v>83.492336422509979</v>
       </c>
       <c r="O2" t="s">
@@ -1752,7 +1739,7 @@
       <c r="A3" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="11">
         <v>0</v>
       </c>
       <c r="C3" s="5">
@@ -1789,7 +1776,7 @@
         <v>24.362225892369995</v>
       </c>
       <c r="N3" s="5">
-        <f>+SUM(B3:M3)</f>
+        <f t="shared" si="0"/>
         <v>90.879313784761649</v>
       </c>
       <c r="P3" s="7"/>
@@ -1835,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <f>+SUM(B4:M4)</f>
+        <f t="shared" si="0"/>
         <v>34.133031362509982</v>
       </c>
       <c r="Q4" s="7">
@@ -1884,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="5">
-        <f>+SUM(B5:M5)</f>
+        <f t="shared" si="0"/>
         <v>49.359305059999997</v>
       </c>
       <c r="Q5" s="7">
@@ -1921,7 +1908,8 @@
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>4.0619130575</v>
+        <f>4.0619130575+0.0272368961616536</f>
+        <v>4.0891499536616536</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
@@ -1933,8 +1921,8 @@
         <v>0</v>
       </c>
       <c r="N6" s="5">
-        <f>+SUM(B6:M6)</f>
-        <v>73.464109063600006</v>
+        <f t="shared" si="0"/>
+        <v>73.491345959761674</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.15">
@@ -1978,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="5">
-        <f>+SUM(B7:M7)</f>
+        <f t="shared" si="0"/>
         <v>36.953714519999998</v>
       </c>
     </row>
@@ -2023,7 +2011,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="5">
-        <f>+SUM(B8:M8)</f>
+        <f t="shared" si="0"/>
         <v>15.874814386000001</v>
       </c>
     </row>
@@ -2068,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="5">
-        <f>+SUM(B9:M9)</f>
+        <f t="shared" si="0"/>
         <v>7.4808834299999996</v>
       </c>
     </row>
@@ -2095,7 +2083,8 @@
         <v>1.5233916200000002</v>
       </c>
       <c r="H10" s="5">
-        <v>2.5385214375</v>
+        <f>2.5385214375+0.0272368961616536</f>
+        <v>2.5657583336616536</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -2113,8 +2102,8 @@
         <v>0</v>
       </c>
       <c r="N10" s="5">
-        <f>+SUM(B10:M10)</f>
-        <v>4.0619130575</v>
+        <f t="shared" si="0"/>
+        <v>4.0891499536616536</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.15">
@@ -2158,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="5">
-        <f>+SUM(B11:M11)</f>
+        <f t="shared" si="0"/>
         <v>5.8828657</v>
       </c>
     </row>
@@ -2203,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="5">
-        <f>+SUM(B12:M12)</f>
+        <f t="shared" si="0"/>
         <v>7.3869768858900002</v>
       </c>
       <c r="Q12" s="7">
@@ -2252,7 +2241,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="5">
-        <f>+SUM(B13:M13)</f>
+        <f t="shared" si="0"/>
         <v>24.362225894000002</v>
       </c>
     </row>
@@ -2261,51 +2250,51 @@
         <v>21</v>
       </c>
       <c r="B14" s="5">
-        <f>+SUM(B2:B13)</f>
+        <f t="shared" ref="B14:M14" si="1">+SUM(B2:B13)</f>
         <v>83.492336422509979</v>
       </c>
       <c r="C14" s="5">
-        <f>+SUM(C2:C13)</f>
+        <f t="shared" si="1"/>
         <v>90.879313308399986</v>
       </c>
       <c r="D14" s="5">
-        <f>+SUM(D2:D13)</f>
+        <f t="shared" si="1"/>
         <v>34.133031370000005</v>
       </c>
       <c r="E14" s="5">
-        <f>+SUM(E2:E13)</f>
+        <f t="shared" si="1"/>
         <v>49.359305090000007</v>
       </c>
       <c r="F14" s="5">
-        <f>+SUM(F2:F13)</f>
+        <f t="shared" si="1"/>
         <v>73.491345959761659</v>
       </c>
       <c r="G14" s="5">
-        <f>+SUM(G2:G13)</f>
+        <f t="shared" si="1"/>
         <v>36.953714519999998</v>
       </c>
       <c r="H14" s="5">
-        <f>+SUM(H2:H13)</f>
-        <v>15.847577930230001</v>
+        <f t="shared" si="1"/>
+        <v>15.874814826391654</v>
       </c>
       <c r="I14" s="5">
-        <f>+SUM(I2:I13)</f>
+        <f t="shared" si="1"/>
         <v>7.4808834300000004</v>
       </c>
       <c r="J14" s="5">
-        <f>+SUM(J2:J13)</f>
-        <v>4.0619130575</v>
+        <f t="shared" si="1"/>
+        <v>4.0891499536616536</v>
       </c>
       <c r="K14" s="5">
-        <f>+SUM(K2:K13)</f>
+        <f t="shared" si="1"/>
         <v>5.8828657</v>
       </c>
       <c r="L14" s="5">
-        <f>+SUM(L2:L13)</f>
+        <f t="shared" si="1"/>
         <v>7.3869768860000002</v>
       </c>
       <c r="M14" s="5">
-        <f>+SUM(M2:M13)</f>
+        <f t="shared" si="1"/>
         <v>24.362225892369995</v>
       </c>
       <c r="N14" s="5">
@@ -2327,7 +2316,7 @@
         <v>49.359305059999997</v>
       </c>
       <c r="F16">
-        <v>73.464109063600006</v>
+        <v>73.491345959761674</v>
       </c>
       <c r="G16">
         <v>36.953714519999998</v>
@@ -2339,7 +2328,7 @@
         <v>7.4808834299999996</v>
       </c>
       <c r="J16">
-        <v>4.0619130575</v>
+        <v>4.0891499536616536</v>
       </c>
       <c r="K16">
         <v>5.8828657</v>
@@ -2349,6 +2338,56 @@
       </c>
       <c r="M16">
         <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B17" s="12">
+        <f>+B14-B16</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" ref="C17:M17" si="2">+C14-C16</f>
+        <v>-4.7636166300435434E-7</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="2"/>
+        <v>7.4900228241858713E-9</v>
+      </c>
+      <c r="E17" s="12">
+        <f t="shared" si="2"/>
+        <v>3.0000009587638488E-8</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <f t="shared" si="2"/>
+        <v>4.4039165381093426E-7</v>
+      </c>
+      <c r="I17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1000000910144081E-10</v>
+      </c>
+      <c r="M17" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.6300063521157426E-9</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.15">
@@ -2357,47 +2396,47 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" ref="C18:M18" si="0">ROUND(C14-C16,1)</f>
+        <f t="shared" ref="C18:M18" si="3">ROUND(C14-C16,1)</f>
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -2426,7 +2465,7 @@
       <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>194</v>
       </c>
       <c r="D22" s="7"/>
@@ -2434,7 +2473,7 @@
       <c r="F22" s="7"/>
       <c r="J22" s="7">
         <f>+J6-C39</f>
-        <v>4.0619130575</v>
+        <v>4.0891499536616536</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.15">
@@ -2442,12 +2481,15 @@
       <c r="H23" s="7"/>
       <c r="J23" s="7">
         <f>+H10-C39</f>
-        <v>2.5385214375</v>
+        <v>2.5657583336616536</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B25">
         <v>1000000</v>
+      </c>
+      <c r="F25">
+        <v>2.723689616165359E-2</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.15">
@@ -2628,33 +2670,33 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:N14">
-    <cfRule type="cellIs" dxfId="25" priority="7" operator="notEqual">
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B45">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:B55">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B18:M18">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B45">
-    <cfRule type="cellIs" dxfId="22" priority="3" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53:B55">
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="cellIs" dxfId="20" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="B2:N14">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2664,7 +2706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Y71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2760,10 +2802,10 @@
       <c r="E2" s="5">
         <v>14.341871281889999</v>
       </c>
-      <c r="F2" s="12">
-        <v>0</v>
-      </c>
-      <c r="G2" s="12">
+      <c r="F2" s="11">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
         <v>0</v>
       </c>
       <c r="H2" s="5">
@@ -2832,13 +2874,13 @@
       <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="11">
         <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>19.770212353719991</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>0</v>
       </c>
       <c r="H3" s="5">
@@ -2907,10 +2949,10 @@
       <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4" s="12">
-        <v>0</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
         <v>0</v>
       </c>
       <c r="G4" s="5">
@@ -2970,13 +3012,13 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12">
-        <v>0</v>
-      </c>
-      <c r="C5" s="12">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
         <v>0</v>
       </c>
       <c r="E5" s="5">
@@ -3028,7 +3070,7 @@
       <c r="U5" s="5">
         <v>0.16482158305</v>
       </c>
-      <c r="V5" s="12"/>
+      <c r="V5" s="11"/>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
         <v>14.60937084733</v>
@@ -3042,13 +3084,13 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12">
-        <v>0</v>
-      </c>
-      <c r="C6" s="12">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
         <v>0</v>
       </c>
       <c r="E6" s="5">
@@ -3100,7 +3142,7 @@
       <c r="U6" s="5">
         <v>20.612622200999997</v>
       </c>
-      <c r="V6" s="12"/>
+      <c r="V6" s="11"/>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
         <v>24.824325021429996</v>
@@ -3114,13 +3156,13 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12">
-        <v>0</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
         <v>0</v>
       </c>
       <c r="E7" s="5">
@@ -3172,7 +3214,7 @@
       <c r="U7" s="5">
         <v>3.5847821083199998</v>
       </c>
-      <c r="V7" s="12"/>
+      <c r="V7" s="11"/>
       <c r="W7" s="5">
         <f t="shared" si="0"/>
         <v>51.445617916001666</v>
@@ -3514,12 +3556,12 @@
       <c r="O12" s="5">
         <v>5.8828657</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
       <c r="R12" s="5">
         <v>7.3869768860000002</v>
       </c>
-      <c r="S12" s="12"/>
+      <c r="S12" s="11"/>
       <c r="T12" s="5">
         <v>0</v>
       </c>
@@ -3754,9 +3796,9 @@
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="5">
         <v>0</v>
       </c>
@@ -3823,7 +3865,7 @@
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="C17" s="12"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="5">
         <v>0</v>
       </c>
@@ -3974,9 +4016,9 @@
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="5">
         <v>0</v>
       </c>
@@ -4040,11 +4082,11 @@
       <c r="D20" s="5">
         <v>0</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
       <c r="J20" s="5">
         <v>0</v>
       </c>
@@ -4147,7 +4189,7 @@
       <c r="S21" s="5">
         <v>0</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="T21" s="11"/>
       <c r="U21" s="5">
         <v>0</v>
       </c>
@@ -4220,7 +4262,7 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="12"/>
+      <c r="U22" s="11"/>
       <c r="V22" s="5">
         <v>0</v>
       </c>
@@ -4492,7 +4534,7 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>178</v>
       </c>
       <c r="H31" s="7"/>
@@ -4794,38 +4836,33 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="notEqual">
+  <conditionalFormatting sqref="B29:D29">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:D54">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62:D64">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69:D69">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:D29">
-    <cfRule type="cellIs" dxfId="16" priority="4" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:D54">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B62:D64">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B69:D69">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4835,7 +4872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Y58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5141,9 +5178,9 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="5">
         <v>0</v>
       </c>
@@ -5193,7 +5230,7 @@
       <c r="U5" s="5">
         <v>0.16482158305</v>
       </c>
-      <c r="V5" s="12"/>
+      <c r="V5" s="11"/>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
         <v>14.60937084733</v>
@@ -5207,9 +5244,9 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
       <c r="E6" s="5">
         <v>0</v>
       </c>
@@ -5259,7 +5296,7 @@
       <c r="U6" s="5">
         <v>20.612622200999997</v>
       </c>
-      <c r="V6" s="12"/>
+      <c r="V6" s="11"/>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
         <v>24.824325021429996</v>
@@ -5273,9 +5310,9 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
       <c r="E7" s="5">
         <v>0</v>
       </c>
@@ -5325,7 +5362,7 @@
       <c r="U7" s="5">
         <v>3.5847821083199998</v>
       </c>
-      <c r="V7" s="12"/>
+      <c r="V7" s="11"/>
       <c r="W7" s="5">
         <f t="shared" si="0"/>
         <v>51.445617916001666</v>
@@ -5667,12 +5704,12 @@
       <c r="O12" s="5">
         <v>5.8828657</v>
       </c>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
       <c r="R12" s="5">
         <v>7.3869768860000002</v>
       </c>
-      <c r="S12" s="12"/>
+      <c r="S12" s="11"/>
       <c r="T12" s="5">
         <v>0</v>
       </c>
@@ -5907,9 +5944,9 @@
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
       <c r="E16" s="5">
         <v>0</v>
       </c>
@@ -5976,7 +6013,7 @@
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="C17" s="12"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="5">
         <v>0</v>
       </c>
@@ -6127,9 +6164,9 @@
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="5">
         <v>0</v>
       </c>
@@ -6193,11 +6230,11 @@
       <c r="D20" s="5">
         <v>0</v>
       </c>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
       <c r="J20" s="5">
         <v>0</v>
       </c>
@@ -6300,7 +6337,7 @@
       <c r="S21" s="5">
         <v>0</v>
       </c>
-      <c r="T21" s="12"/>
+      <c r="T21" s="11"/>
       <c r="U21" s="5">
         <v>0</v>
       </c>
@@ -6373,7 +6410,7 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="12"/>
+      <c r="U22" s="11"/>
       <c r="V22" s="5">
         <v>0</v>
       </c>
@@ -6645,7 +6682,7 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>178</v>
       </c>
       <c r="H31" s="7"/>
@@ -6836,21 +6873,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B29:D29">
     <cfRule type="cellIs" dxfId="9" priority="2" operator="notEqual">
       <formula>0</formula>
@@ -6861,13 +6883,23 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -8773,7 +8805,7 @@
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>178</v>
       </c>
     </row>
@@ -8788,23 +8820,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="B29:D29">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:D29">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8814,7 +8841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AA177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -11533,7 +11560,7 @@
       <c r="E97" t="s">
         <v>154</v>
       </c>
-      <c r="H97" s="10"/>
+      <c r="H97" s="9"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" t="s">
@@ -11821,7 +11848,7 @@
       <c r="B133" t="s">
         <v>161</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="8">
         <f>+E2</f>
         <v>28.80303928</v>
       </c>
@@ -11848,7 +11875,7 @@
       <c r="B136" t="s">
         <v>164</v>
       </c>
-      <c r="E136" s="8">
+      <c r="E136" s="7">
         <f>+E3</f>
         <v>0.17356569899999999</v>
       </c>
@@ -12218,23 +12245,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="notEqual">
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="J50">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/macro_sam_2008_analisis.xlsx
+++ b/macro_sam_2008_analisis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\francisco.henriquez\Mis documentos\proyectos\equilibrio_general\eq_general\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF307187-9196-4FAD-95DC-7A6E6674C675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9BA6AE-4475-47CE-BA8B-033AB67F8FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId1"/>
@@ -19,6 +19,41 @@
     <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId4"/>
     <sheet name="macro_sam_2008" sheetId="1" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$F$67</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">0.7</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.3</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="197">
   <si>
     <t>Act prim</t>
   </si>
@@ -622,6 +657,12 @@
   </si>
   <si>
     <t>Esta el la SAM que se está utilizando, con un solo producto producido en una sola actividad</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>gamma</t>
   </si>
 </sst>
 </file>
@@ -631,7 +672,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1140,7 +1181,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1633,7 +1674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="4" width="12.5" bestFit="1" customWidth="1"/>
@@ -2667,6 +2708,64 @@
       <c r="B62" s="7">
         <f>+B60-B59</f>
         <v>1.1501183518899984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A65" s="7" t="str">
+        <f>+A4</f>
+        <v>Trabajo</v>
+      </c>
+      <c r="B65" s="7">
+        <f>+B4</f>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A66" s="7" t="str">
+        <f>+A5</f>
+        <v>Capital</v>
+      </c>
+      <c r="B66" s="7">
+        <f>+B5</f>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A67" s="7" t="str">
+        <f>+A14</f>
+        <v>Total</v>
+      </c>
+      <c r="B67" s="7">
+        <f>+B14</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="D67">
+        <f>B70*(65^B69)*(B66^(1-B69))</f>
+        <v>83.492336404101223</v>
+      </c>
+      <c r="F67" s="7">
+        <f>+B67-D67</f>
+        <v>1.8408755408927391E-8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69">
+        <v>0.43654369057980391</v>
+      </c>
+      <c r="D69">
+        <f>1-B69</f>
+        <v>0.56345630942019609</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/macro_sam_2008_analisis.xlsx
+++ b/macro_sam_2008_analisis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\francisco.henriquez\Mis documentos\proyectos\equilibrio_general\eq_general\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9BA6AE-4475-47CE-BA8B-033AB67F8FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A674702F-C876-41B9-8C9D-D2FD2EDF3154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="19440" windowHeight="15000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId1"/>
@@ -36,7 +36,7 @@
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$F$67</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$F$71</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="198">
   <si>
     <t>Act prim</t>
   </si>
@@ -663,6 +663,9 @@
   </si>
   <si>
     <t>gamma</t>
+  </si>
+  <si>
+    <t>tasa vat</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="4" width="12.5" bestFit="1" customWidth="1"/>
@@ -2710,7 +2713,7 @@
         <v>1.1501183518899984</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A65" s="7" t="str">
         <f>+A4</f>
         <v>Trabajo</v>
@@ -2720,7 +2723,7 @@
         <v>34.133031362509982</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A66" s="7" t="str">
         <f>+A5</f>
         <v>Capital</v>
@@ -2730,7 +2733,7 @@
         <v>49.359305059999997</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A67" s="7" t="str">
         <f>+A14</f>
         <v>Total</v>
@@ -2740,32 +2743,63 @@
         <v>83.492336422509979</v>
       </c>
       <c r="D67">
-        <f>B70*(65^B69)*(B66^(1-B69))</f>
-        <v>83.492336404101223</v>
+        <f>B70*(B65^B69)*(B66^(1-B69))</f>
+        <v>83.492336422509979</v>
       </c>
       <c r="F67" s="7">
         <f>+B67-D67</f>
-        <v>1.8408755408927391E-8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <f>(B65^B69)*(B66^D69)</f>
+        <v>41.746166797763046</v>
+      </c>
+      <c r="J67">
+        <f>+B67/H67</f>
+        <v>2.0000000677184064</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>195</v>
       </c>
       <c r="B69">
-        <v>0.43654369057980391</v>
+        <v>0.45415154287117893</v>
       </c>
       <c r="D69">
         <f>1-B69</f>
-        <v>0.56345630942019609</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.54584845712882113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>196</v>
       </c>
       <c r="B70">
-        <v>1.5</v>
+        <f>+J67</f>
+        <v>2.0000000677184064</v>
+      </c>
+      <c r="F70">
+        <f>+B70*B69*(B66^D69)*(B65^(B69-1))</f>
+        <v>1.1108938143082672</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="F71">
+        <f>+D69*B70*(B66^(D69-1))*(B65^B69)</f>
+        <v>0.92331451917543572</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D75">
+        <f>7.5+8.8+56</f>
+        <v>72.3</v>
       </c>
     </row>
   </sheetData>

--- a/macro_sam_2008_analisis.xlsx
+++ b/macro_sam_2008_analisis.xlsx
@@ -1,26 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\francisco.henriquez\Mis documentos\proyectos\equilibrio_general\eq_general\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A674702F-C876-41B9-8C9D-D2FD2EDF3154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11310"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId1"/>
-    <sheet name="macro_sam_2008" sheetId="1" r:id="rId2"/>
+    <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId1"/>
+    <sheet name="macro_sam_2008__simp_1" sheetId="10" r:id="rId2"/>
+    <sheet name="macro_sam_2008__simp" sheetId="9" r:id="rId3"/>
+    <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId4"/>
+    <sheet name="macro_sam_2008" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$F$71</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">0.7</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.3</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="198">
   <si>
     <t>Act prim</t>
   </si>
@@ -560,15 +612,70 @@
   </si>
   <si>
     <t>La producción no tiene IVA</t>
+  </si>
+  <si>
+    <t>pasar las exportaciones al consumo de los hogares</t>
+  </si>
+  <si>
+    <t>pasar los ingresos del capital y el trabajo row a los hogares</t>
+  </si>
+  <si>
+    <t>Quitar del consumo de los hogares lo que se importa</t>
+  </si>
+  <si>
+    <t>pasar SI row a hogares</t>
+  </si>
+  <si>
+    <t>qiotar ingresos del capital de row y de lo que el capital le transfiere a los hogares</t>
+  </si>
+  <si>
+    <t>quitar el arancel de los productos que consumen los hogares, quitarlo de los ingresos del gobierno y disminuir en ese monto las transferencias a los hogares</t>
+  </si>
+  <si>
+    <t>quitar el impuesto especifico a la actividad manufacturera y wal prod manu de esa actividad</t>
+  </si>
+  <si>
+    <t>quitar ese monto al consumo de los hogares de prod manu</t>
+  </si>
+  <si>
+    <t>quitar ese monto de los ingresos del gob y de las transferencias a los hogares</t>
+  </si>
+  <si>
+    <t>El impuesto a los productos se elimina de cada producto, lo que se descuenta del consumo de los hogares, lo que a su vez se resta de las prestaciones sociales que recibe del gobierno</t>
+  </si>
+  <si>
+    <t>Se elimina el gasto intermedio en productos, el que se asigna al prod principal de cada actvidad y se cuadra la diferencia con hogares</t>
+  </si>
+  <si>
+    <t>Hacer que cada sector produzca un solo bien</t>
+  </si>
+  <si>
+    <t>Act</t>
+  </si>
+  <si>
+    <t>Prod</t>
+  </si>
+  <si>
+    <t>Esta el la SAM que se está utilizando, con un solo producto producido en una sola actividad</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>tasa vat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1064,7 +1171,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1073,10 +1180,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1123,7 +1231,86 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1170,12 +1357,40 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1461,7 +1676,5363 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="4" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>83.492336422509979</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <f t="shared" ref="N2:N13" si="0">+SUM(B2:M2)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="O2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>+SUM(C2:C2)</f>
+        <v>83.492336422509979</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>56.02172243576166</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10.495365456630001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>24.362225892369995</v>
+      </c>
+      <c r="N3" s="5">
+        <f t="shared" si="0"/>
+        <v>90.879313784761649</v>
+      </c>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34.133031362509982</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <f t="shared" si="0"/>
+        <v>34.133031362509982</v>
+      </c>
+      <c r="Q4" s="7">
+        <f>+SUM(B4:B4)</f>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <f t="shared" si="0"/>
+        <v>49.359305059999997</v>
+      </c>
+      <c r="Q5" s="7">
+        <f>+SUM(B5:B5)</f>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>34.133031370000005</v>
+      </c>
+      <c r="E6" s="5">
+        <v>17.281502200000006</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>17.431284399999999</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.55637803610000003</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <f>4.0619130575+0.0272368961616536</f>
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="0"/>
+        <v>73.491345959761674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>31.096709390000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5.8570051300000001</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <f t="shared" si="0"/>
+        <v>36.953714519999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.98109349999999995</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1.6238783000000001</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>5.8828657</v>
+      </c>
+      <c r="L8" s="5">
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <f t="shared" si="0"/>
+        <v>15.874814386000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4808834299999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1.5233916200000002</v>
+      </c>
+      <c r="H10" s="5">
+        <f>2.5385214375+0.0272368961616536</f>
+        <v>2.5657583336616536</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" si="0"/>
+        <v>4.0891499536616536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1.2089669999999999</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4.6738986999999996</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8828657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="Q12" s="7">
+        <f>+SUM(C12:C12)</f>
+        <v>7.3869768858900002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>8.7797730940000012</v>
+      </c>
+      <c r="G13" s="5">
+        <v>13.325139800000001</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2.2573129999999999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <f t="shared" si="0"/>
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
+        <f t="shared" ref="B14:M14" si="1">+SUM(B2:B13)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" si="1"/>
+        <v>90.879313308399986</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="1"/>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="1"/>
+        <v>49.359305090000007</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="1"/>
+        <v>73.491345959761659</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="1"/>
+        <v>36.953714519999998</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="1"/>
+        <v>15.874814826391654</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="1"/>
+        <v>7.4808834300000004</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="1"/>
+        <v>5.8828657</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="1"/>
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="1"/>
+        <v>24.362225892369995</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B16">
+        <f t="array" ref="B16:M16">TRANSPOSE(N2:N13)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="C16">
+        <v>90.879313784761649</v>
+      </c>
+      <c r="D16">
+        <v>34.133031362509982</v>
+      </c>
+      <c r="E16">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="F16">
+        <v>73.491345959761674</v>
+      </c>
+      <c r="G16">
+        <v>36.953714519999998</v>
+      </c>
+      <c r="H16">
+        <v>15.874814386000001</v>
+      </c>
+      <c r="I16">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="J16">
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K16">
+        <v>5.8828657</v>
+      </c>
+      <c r="L16">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="M16">
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B17" s="12">
+        <f>+B14-B16</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="12">
+        <f t="shared" ref="C17:M17" si="2">+C14-C16</f>
+        <v>-4.7636166300435434E-7</v>
+      </c>
+      <c r="D17" s="12">
+        <f t="shared" si="2"/>
+        <v>7.4900228241858713E-9</v>
+      </c>
+      <c r="E17" s="12">
+        <f t="shared" si="2"/>
+        <v>3.0000009587638488E-8</v>
+      </c>
+      <c r="F17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="12">
+        <f t="shared" si="2"/>
+        <v>4.4039165381093426E-7</v>
+      </c>
+      <c r="I17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" si="2"/>
+        <v>1.1000000910144081E-10</v>
+      </c>
+      <c r="M17" s="12">
+        <f t="shared" si="2"/>
+        <v>-1.6300063521157426E-9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B18" s="2">
+        <f>ROUND(B14-B16,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" ref="C18:M18" si="3">ROUND(C14-C16,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>12733.68651</v>
+      </c>
+      <c r="F20" s="7">
+        <f>+SUM(F3:F3)</f>
+        <v>56.02172243576166</v>
+      </c>
+      <c r="H20" s="7">
+        <f>+SUM(H3:H3)</f>
+        <v>10.495365456630001</v>
+      </c>
+      <c r="M20" s="7">
+        <f>+SUM(M3:M3)</f>
+        <v>24.362225892369995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A22" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="J22" s="7">
+        <f>+J6-C39</f>
+        <v>4.0891499536616536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="F23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="J23" s="7">
+        <f>+H10-C39</f>
+        <v>2.5657583336616536</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <v>1000000</v>
+      </c>
+      <c r="F25">
+        <v>2.723689616165359E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="5">
+        <v>3.1605375580000001</v>
+      </c>
+      <c r="D43" s="7" t="e">
+        <f>+#REF!-B47</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F43" s="7" t="e">
+        <f>+F3+D43</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="5">
+        <v>6.9137747879999996</v>
+      </c>
+      <c r="D44" s="7" t="e">
+        <f>+#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7" t="e">
+        <f>+#REF!+D44</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="5">
+        <v>4.4456911320000003</v>
+      </c>
+      <c r="D45" s="7" t="e">
+        <f>+#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F45" s="7" t="e">
+        <f>+#REF!+D45</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="7">
+        <f>+SUM(B43:B45)</f>
+        <v>14.520003478</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B49" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B52" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="5">
+        <v>14.16830558289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="5">
+        <v>0.17356569899999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B57" s="7">
+        <f>+SUM(B53:B55)</f>
+        <v>14.341871281889999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B59" s="7">
+        <v>1.8377085351100018</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="5">
+        <v>2.9878268870000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B62" s="7">
+        <f>+B60-B59</f>
+        <v>1.1501183518899984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A65" s="7" t="str">
+        <f>+A4</f>
+        <v>Trabajo</v>
+      </c>
+      <c r="B65" s="7">
+        <f>+B4</f>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A66" s="7" t="str">
+        <f>+A5</f>
+        <v>Capital</v>
+      </c>
+      <c r="B66" s="7">
+        <f>+B5</f>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A67" s="7" t="str">
+        <f>+A14</f>
+        <v>Total</v>
+      </c>
+      <c r="B67" s="7">
+        <f>+B14</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="D67">
+        <f>B70*(B65^B69)*(B66^(1-B69))</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="F67" s="7">
+        <f>+B67-D67</f>
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <f>(B65^B69)*(B66^D69)</f>
+        <v>41.746166797763046</v>
+      </c>
+      <c r="J67">
+        <f>+B67/H67</f>
+        <v>2.0000000677184064</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>195</v>
+      </c>
+      <c r="B69">
+        <v>0.45415154287117893</v>
+      </c>
+      <c r="D69">
+        <f>1-B69</f>
+        <v>0.54584845712882113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>196</v>
+      </c>
+      <c r="B70">
+        <f>+J67</f>
+        <v>2.0000000677184064</v>
+      </c>
+      <c r="F70">
+        <f>+B70*B69*(B66^D69)*(B65^(B69-1))</f>
+        <v>1.1108938143082672</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="F71">
+        <f>+D69*B70*(B66^(D69-1))*(B65^B69)</f>
+        <v>0.92331451917543572</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>197</v>
+      </c>
+      <c r="B75">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D75">
+        <f>7.5+8.8+56</f>
+        <v>72.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B45">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:B55">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:M18">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:N14">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Y71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="12" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="12" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>14.341871281889999</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <f>+SUM(B2:V2)</f>
+        <v>14.341871281889999</v>
+      </c>
+      <c r="X2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>19.770212353719991</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5">
+        <f t="shared" ref="W3:W22" si="0">+SUM(B3:V3)</f>
+        <v>19.770212353719991</v>
+      </c>
+      <c r="X3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>49.380252786899987</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
+        <f t="shared" si="0"/>
+        <v>49.380252786899987</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>14.427016289780001</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.75329745E-2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5">
+        <v>0.16482158305</v>
+      </c>
+      <c r="V5" s="11"/>
+      <c r="W5" s="5">
+        <f t="shared" si="0"/>
+        <v>14.60937084733</v>
+      </c>
+      <c r="Y5" s="7">
+        <f>+T5+J5</f>
+        <v>14.427016289780001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4.1279825582999976</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>8.3720262130000001E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5">
+        <v>20.612622200999997</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="5">
+        <f t="shared" si="0"/>
+        <v>24.824325021429996</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" ref="Y6:Y7" si="1">+T6+J6</f>
+        <v>4.1279825582999976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>37.466723587681663</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>10.39411222</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5">
+        <v>3.5847821083199998</v>
+      </c>
+      <c r="V7" s="11"/>
+      <c r="W7" s="5">
+        <f t="shared" si="0"/>
+        <v>51.445617916001666</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="1"/>
+        <v>37.466723587681663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1.1501183518899984</v>
+      </c>
+      <c r="C8" s="5">
+        <v>8.174254673719993</v>
+      </c>
+      <c r="D8" s="5">
+        <v>24.808658336899988</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" si="0"/>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <v>13.19175293</v>
+      </c>
+      <c r="C9" s="5">
+        <v>11.59595768</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24.571594449999999</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
+        <f t="shared" si="0"/>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>34.133031370000005</v>
+      </c>
+      <c r="I10" s="5">
+        <v>17.281502200000006</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>17.431284399999999</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.55637803610000003</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4.0619130575</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <f t="shared" si="0"/>
+        <v>73.464109063600006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>31.096709390000001</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>5.8570051300000001</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" si="0"/>
+        <v>36.953714519999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.98109349999999995</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1.6238783000000001</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>5.8828657</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="5">
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" si="0"/>
+        <v>15.874814386000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4808834299999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1.5233916200000002</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2.5385214375</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5">
+        <f t="shared" si="0"/>
+        <v>4.0619130575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1.2089669999999999</v>
+      </c>
+      <c r="K15" s="5">
+        <v>4.6738986999999996</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8828657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f>(254765.8734+B29)/1000000</f>
+        <v>0.26749955991000002</v>
+      </c>
+      <c r="F18" s="5">
+        <f>(5033784.004+C29)/1000000</f>
+        <v>5.0541126654799999</v>
+      </c>
+      <c r="G18" s="5">
+        <f>(578585.5105+D29)/1000000</f>
+        <v>2.0653646604999998</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3869768858900002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>8.7797730940000012</v>
+      </c>
+      <c r="K21" s="5">
+        <v>13.325139800000001</v>
+      </c>
+      <c r="L21" s="5">
+        <v>2.2573129999999999</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11"/>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
+        <f t="shared" si="0"/>
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11"/>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5">
+        <f>+SUM(B2:B22)</f>
+        <v>14.341871281889999</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" ref="C23:V23" si="2">+SUM(C2:C22)</f>
+        <v>19.770212353719991</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="2"/>
+        <v>49.380252786899987</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="2"/>
+        <v>14.609370841799999</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="2"/>
+        <v>24.824325019199989</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="2"/>
+        <v>51.445617447399989</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="2"/>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="2"/>
+        <v>49.359305090000007</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="2"/>
+        <v>73.491345959761659</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="2"/>
+        <v>36.953714519999998</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>15.847577930230001</v>
+      </c>
+      <c r="M23" s="5">
+        <f t="shared" si="2"/>
+        <v>7.4808834300000004</v>
+      </c>
+      <c r="N23" s="5">
+        <f t="shared" si="2"/>
+        <v>4.0619130575</v>
+      </c>
+      <c r="O23" s="5">
+        <f t="shared" si="2"/>
+        <v>5.8828657</v>
+      </c>
+      <c r="P23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="2"/>
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="2"/>
+        <v>24.362225892369995</v>
+      </c>
+      <c r="V23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <f t="array" ref="B25:V25">TRANSPOSE(W2:W22)</f>
+        <v>14.341871281889999</v>
+      </c>
+      <c r="C25">
+        <v>19.770212353719991</v>
+      </c>
+      <c r="D25">
+        <v>49.380252786899987</v>
+      </c>
+      <c r="E25">
+        <v>14.60937084733</v>
+      </c>
+      <c r="F25">
+        <v>24.824325021429996</v>
+      </c>
+      <c r="G25">
+        <v>51.445617916001666</v>
+      </c>
+      <c r="H25">
+        <v>34.133031362509982</v>
+      </c>
+      <c r="I25">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="J25">
+        <v>73.464109063600006</v>
+      </c>
+      <c r="K25">
+        <v>36.953714519999998</v>
+      </c>
+      <c r="L25">
+        <v>15.874814386000001</v>
+      </c>
+      <c r="M25">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="N25">
+        <v>4.0619130575</v>
+      </c>
+      <c r="O25">
+        <v>5.8828657</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>24.362225894000002</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B27" s="2">
+        <f>ROUND(B23-B25,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" ref="C27:V27" si="3">ROUND(C23-C25,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="5">
+        <v>12733.68651</v>
+      </c>
+      <c r="C29" s="5">
+        <v>20328.661479999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1486779.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A31" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="N31" s="7">
+        <f>+N10-E48</f>
+        <v>4.0619130575</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="F32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="N32" s="7">
+        <f>+L14-E48</f>
+        <v>2.5385214375</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B34">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B42" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B45" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B46" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5">
+        <v>3.1605375580000001</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.927984220000001</v>
+      </c>
+      <c r="D52" s="5">
+        <v>0.16408898730000002</v>
+      </c>
+      <c r="F52" s="7">
+        <f>+SUM(B52:D52)</f>
+        <v>15.2526107653</v>
+      </c>
+      <c r="H52" s="7">
+        <f>+F52-B56</f>
+        <v>0.73260728730000046</v>
+      </c>
+      <c r="J52" s="7">
+        <f>+J5+H52</f>
+        <v>15.159623577080001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="5">
+        <v>6.9137747879999996</v>
+      </c>
+      <c r="C53" s="5">
+        <v>22.11542081</v>
+      </c>
+      <c r="D53" s="5">
+        <v>11.39658985</v>
+      </c>
+      <c r="F53" s="7">
+        <f t="shared" ref="F53:F54" si="4">+SUM(B53:D53)</f>
+        <v>40.425785447999999</v>
+      </c>
+      <c r="H53" s="7">
+        <f>+F53-C56</f>
+        <v>-3.8729534620000052</v>
+      </c>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7">
+        <f t="shared" ref="J53:J54" si="5">+J6+H53</f>
+        <v>0.25502909629999237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="5">
+        <v>4.4456911320000003</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10.25533388</v>
+      </c>
+      <c r="D54" s="5">
+        <v>25.790391530000001</v>
+      </c>
+      <c r="F54" s="7">
+        <f t="shared" si="4"/>
+        <v>40.491416542000003</v>
+      </c>
+      <c r="H54" s="7">
+        <f>+F54-D56</f>
+        <v>3.1403461747000065</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="5"/>
+        <v>40.60706976238167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B56" s="7">
+        <f>+SUM(B52:B54)</f>
+        <v>14.520003478</v>
+      </c>
+      <c r="C56" s="7">
+        <f t="shared" ref="C56:D56" si="6">+SUM(C52:C54)</f>
+        <v>44.298738910000004</v>
+      </c>
+      <c r="D56" s="7">
+        <f t="shared" si="6"/>
+        <v>37.351070367299997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B60" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A62" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B62" s="5">
+        <v>14.16830558289</v>
+      </c>
+      <c r="C62" s="5">
+        <v>1.069724034</v>
+      </c>
+      <c r="D62" s="5">
+        <v>0.94155019620000002</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A63" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" s="5">
+        <v>0.17356569899999999</v>
+      </c>
+      <c r="C63" s="5">
+        <v>17.205046675719991</v>
+      </c>
+      <c r="D63" s="5">
+        <v>1.318426093</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" s="5">
+        <v>0</v>
+      </c>
+      <c r="C64" s="5">
+        <v>1.495441644</v>
+      </c>
+      <c r="D64" s="5">
+        <v>47.12027649769999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B66" s="7">
+        <f>+SUM(B62:B64)</f>
+        <v>14.341871281889999</v>
+      </c>
+      <c r="C66" s="7">
+        <f t="shared" ref="C66:D66" si="7">+SUM(C62:C64)</f>
+        <v>19.770212353719991</v>
+      </c>
+      <c r="D66" s="7">
+        <f t="shared" si="7"/>
+        <v>49.380252786899987</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B68" s="7">
+        <v>1.8377085351100018</v>
+      </c>
+      <c r="C68" s="7">
+        <v>-1.073173883719992</v>
+      </c>
+      <c r="D68" s="7">
+        <v>-0.76453463689998813</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="5">
+        <v>2.9878268870000002</v>
+      </c>
+      <c r="C69" s="5">
+        <v>7.1010807900000001</v>
+      </c>
+      <c r="D69" s="5">
+        <v>24.0441237</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="B71" s="7">
+        <f>+B69-B68</f>
+        <v>1.1501183518899984</v>
+      </c>
+      <c r="C71" s="7">
+        <f t="shared" ref="C71:D71" si="8">+C69-C68</f>
+        <v>8.174254673719993</v>
+      </c>
+      <c r="D71" s="7">
+        <f t="shared" si="8"/>
+        <v>24.808658336899988</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B29:D29">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:D54">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62:D64">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B69:D69">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Y58"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12" hidden="1" customWidth="1"/>
+    <col min="19" max="20" width="12" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="12" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>14.16830558289</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1.069724034</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.94155019620000002</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <f>+SUM(B2:V2)</f>
+        <v>16.179579813090001</v>
+      </c>
+      <c r="X2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.17356569899999999</v>
+      </c>
+      <c r="F3" s="5">
+        <v>17.205046675719991</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1.318426093</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5">
+        <f t="shared" ref="W3:W22" si="0">+SUM(B3:V3)</f>
+        <v>18.697038467719992</v>
+      </c>
+      <c r="X3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1.495441644</v>
+      </c>
+      <c r="G4" s="5">
+        <v>47.12027649769999</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
+        <f t="shared" si="0"/>
+        <v>48.615718141699993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>14.427016289780001</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.75329745E-2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5">
+        <v>0.16482158305</v>
+      </c>
+      <c r="V5" s="11"/>
+      <c r="W5" s="5">
+        <f t="shared" si="0"/>
+        <v>14.60937084733</v>
+      </c>
+      <c r="Y5" s="7">
+        <f>+T5+J5</f>
+        <v>14.427016289780001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>4.1279825582999976</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>8.3720262130000001E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5">
+        <v>20.612622200999997</v>
+      </c>
+      <c r="V6" s="11"/>
+      <c r="W6" s="5">
+        <f t="shared" si="0"/>
+        <v>24.824325021429996</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" ref="Y6:Y7" si="1">+T6+J6</f>
+        <v>4.1279825582999976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>37.466723587681663</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>10.39411222</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5">
+        <v>3.5847821083199998</v>
+      </c>
+      <c r="V7" s="11"/>
+      <c r="W7" s="5">
+        <f t="shared" si="0"/>
+        <v>51.445617916001666</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="1"/>
+        <v>37.466723587681663</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2.9878268870000002</v>
+      </c>
+      <c r="C8" s="5">
+        <v>7.1010807900000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>24.0441237</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <f t="shared" si="0"/>
+        <v>34.133031377000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5">
+        <v>13.19175293</v>
+      </c>
+      <c r="C9" s="5">
+        <v>11.59595768</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24.571594449999999</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
+        <f t="shared" si="0"/>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>34.133031370000005</v>
+      </c>
+      <c r="I10" s="5">
+        <v>17.281502200000006</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>17.431284399999999</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.55637803610000003</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4.0619130575</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <f t="shared" si="0"/>
+        <v>73.464109063600006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>31.096709390000001</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>5.8570051300000001</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" si="0"/>
+        <v>36.953714519999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.98109349999999995</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1.6238783000000001</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
+        <v>5.8828657</v>
+      </c>
+      <c r="P12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="5">
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="S12" s="11"/>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" si="0"/>
+        <v>15.874814386000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4808834299999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>1.5233916200000002</v>
+      </c>
+      <c r="L14" s="5">
+        <v>2.5385214375</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5">
+        <f t="shared" si="0"/>
+        <v>4.0619130575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1.2089669999999999</v>
+      </c>
+      <c r="K15" s="5">
+        <v>4.6738986999999996</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8828657</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11"/>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <f>(254765.8734+B29)/1000000</f>
+        <v>0.26749955991000002</v>
+      </c>
+      <c r="F18" s="5">
+        <f>(5033784.004+C29)/1000000</f>
+        <v>5.0541126654799999</v>
+      </c>
+      <c r="G18" s="5">
+        <f>(578585.5105+D29)/1000000</f>
+        <v>2.0653646604999998</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3869768858900002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>8.7797730940000012</v>
+      </c>
+      <c r="K21" s="5">
+        <v>13.325139800000001</v>
+      </c>
+      <c r="L21" s="5">
+        <v>2.2573129999999999</v>
+      </c>
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="11"/>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
+        <f t="shared" si="0"/>
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="11"/>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5">
+        <f>+SUM(B2:B22)</f>
+        <v>16.179579817</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" ref="C23:V23" si="2">+SUM(C2:C22)</f>
+        <v>18.697038469999999</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="2"/>
+        <v>48.615718149999999</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="2"/>
+        <v>14.609370841799999</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="2"/>
+        <v>24.824325019199989</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="2"/>
+        <v>51.445617447399989</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="2"/>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="2"/>
+        <v>49.359305090000007</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="2"/>
+        <v>73.491345959761659</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="2"/>
+        <v>36.953714519999998</v>
+      </c>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>15.847577930230001</v>
+      </c>
+      <c r="M23" s="5">
+        <f t="shared" si="2"/>
+        <v>7.4808834300000004</v>
+      </c>
+      <c r="N23" s="5">
+        <f t="shared" si="2"/>
+        <v>4.0619130575</v>
+      </c>
+      <c r="O23" s="5">
+        <f t="shared" si="2"/>
+        <v>5.8828657</v>
+      </c>
+      <c r="P23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="2"/>
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="2"/>
+        <v>24.362225892369995</v>
+      </c>
+      <c r="V23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <f t="array" ref="B25:V25">TRANSPOSE(W2:W22)</f>
+        <v>16.179579813090001</v>
+      </c>
+      <c r="C25">
+        <v>18.697038467719992</v>
+      </c>
+      <c r="D25">
+        <v>48.615718141699993</v>
+      </c>
+      <c r="E25">
+        <v>14.60937084733</v>
+      </c>
+      <c r="F25">
+        <v>24.824325021429996</v>
+      </c>
+      <c r="G25">
+        <v>51.445617916001666</v>
+      </c>
+      <c r="H25">
+        <v>34.133031377000002</v>
+      </c>
+      <c r="I25">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="J25">
+        <v>73.464109063600006</v>
+      </c>
+      <c r="K25">
+        <v>36.953714519999998</v>
+      </c>
+      <c r="L25">
+        <v>15.874814386000001</v>
+      </c>
+      <c r="M25">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="N25">
+        <v>4.0619130575</v>
+      </c>
+      <c r="O25">
+        <v>5.8828657</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>24.362225894000002</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="B27" s="2">
+        <f>ROUND(B23-B25,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="2">
+        <f t="shared" ref="C27:V27" si="3">ROUND(C23-C25,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A29" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="5">
+        <v>12733.68651</v>
+      </c>
+      <c r="C29" s="5">
+        <v>20328.661479999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>1486779.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="A31" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="N31" s="7">
+        <f>+N10-E48</f>
+        <v>4.0619130575</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.15">
+      <c r="F32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="N32" s="7">
+        <f>+L14-E48</f>
+        <v>2.5385214375</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B34">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="I35" s="7"/>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B39" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B42" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B45" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B46" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B48" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="C50" s="7"/>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B51" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="5">
+        <v>3.1605375580000001</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.927984220000001</v>
+      </c>
+      <c r="D52" s="5">
+        <v>0.16408898730000002</v>
+      </c>
+      <c r="F52" s="7">
+        <f>+SUM(B52:D52)</f>
+        <v>15.2526107653</v>
+      </c>
+      <c r="H52" s="7">
+        <f>+F52-B56</f>
+        <v>0.73260728730000046</v>
+      </c>
+      <c r="J52" s="7">
+        <f>+J5+H52</f>
+        <v>15.159623577080001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="5">
+        <v>6.9137747879999996</v>
+      </c>
+      <c r="C53" s="5">
+        <v>22.11542081</v>
+      </c>
+      <c r="D53" s="5">
+        <v>11.39658985</v>
+      </c>
+      <c r="F53" s="7">
+        <f t="shared" ref="F53:F54" si="4">+SUM(B53:D53)</f>
+        <v>40.425785447999999</v>
+      </c>
+      <c r="H53" s="7">
+        <f>+F53-C56</f>
+        <v>-3.8729534620000052</v>
+      </c>
+      <c r="I53" s="7"/>
+      <c r="J53" s="7">
+        <f t="shared" ref="J53:J54" si="5">+J6+H53</f>
+        <v>0.25502909629999237</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="5">
+        <v>4.4456911320000003</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10.25533388</v>
+      </c>
+      <c r="D54" s="5">
+        <v>25.790391530000001</v>
+      </c>
+      <c r="F54" s="7">
+        <f t="shared" si="4"/>
+        <v>40.491416542000003</v>
+      </c>
+      <c r="H54" s="7">
+        <f>+F54-D56</f>
+        <v>3.1403461747000065</v>
+      </c>
+      <c r="J54" s="7">
+        <f t="shared" si="5"/>
+        <v>40.60706976238167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B56" s="7">
+        <f>+SUM(B52:B54)</f>
+        <v>14.520003478</v>
+      </c>
+      <c r="C56" s="7">
+        <f t="shared" ref="C56:D56" si="6">+SUM(C52:C54)</f>
+        <v>44.298738910000004</v>
+      </c>
+      <c r="D56" s="7">
+        <f t="shared" si="6"/>
+        <v>37.351070367299997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B58" t="s">
+        <v>190</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B29:D29">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B52:D54">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="7" priority="4" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -3367,7 +8938,7 @@
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3382,23 +8953,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="7" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="B29:D29">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B29:D29">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3407,8 +8973,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AA177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -6127,7 +11693,7 @@
       <c r="E97" t="s">
         <v>154</v>
       </c>
-      <c r="H97" s="10"/>
+      <c r="H97" s="9"/>
     </row>
     <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" t="s">
@@ -6415,7 +11981,7 @@
       <c r="B133" t="s">
         <v>161</v>
       </c>
-      <c r="E133" s="9">
+      <c r="E133" s="8">
         <f>+E2</f>
         <v>28.80303928</v>
       </c>
@@ -6442,7 +12008,7 @@
       <c r="B136" t="s">
         <v>164</v>
       </c>
-      <c r="E136" s="8">
+      <c r="E136" s="7">
         <f>+E3</f>
         <v>0.17356569899999999</v>
       </c>
@@ -6812,23 +12378,18 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="notEqual">
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:W23 W2:W22">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:V22">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="notEqual">
+  <conditionalFormatting sqref="J50">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/macro_sam_2008_analisis.xlsx
+++ b/macro_sam_2008_analisis.xlsx
@@ -1,58 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\francisco.henriquez\Mis documentos\proyectos\equilibrio_general\eq_general\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A674702F-C876-41B9-8C9D-D2FD2EDF3154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D630674-AA3B-4407-B45C-CFBD31E3C727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId1"/>
+    <sheet name="macro_sam_2008_simp_3" sheetId="12" r:id="rId1"/>
     <sheet name="macro_sam_2008__simp_1" sheetId="10" r:id="rId2"/>
-    <sheet name="macro_sam_2008__simp" sheetId="9" r:id="rId3"/>
-    <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId4"/>
-    <sheet name="macro_sam_2008" sheetId="1" r:id="rId5"/>
+    <sheet name="macro_sam_2008__simp_2" sheetId="11" r:id="rId3"/>
+    <sheet name="macro_sam_2008__simp" sheetId="9" r:id="rId4"/>
+    <sheet name="macro_sam_2008_v1" sheetId="7" r:id="rId5"/>
+    <sheet name="macro_sam_2008" sheetId="1" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_adj" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
-    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
-    <definedName name="solver_lhs2" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
-    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">macro_sam_2008__simp_2!$F$71</definedName>
-    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_rhs1" localSheetId="0" hidden="1">0.7</definedName>
-    <definedName name="solver_rhs2" localSheetId="0" hidden="1">0.3</definedName>
-    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="0" hidden="1">3</definedName>
-    <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
+    <definedName name="solver_adj" localSheetId="2" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="2" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_lhs2" localSheetId="2" hidden="1">macro_sam_2008__simp_2!$B$69</definedName>
+    <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">macro_sam_2008__simp_2!$F$71</definedName>
+    <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_rhs1" localSheetId="2" hidden="1">0.7</definedName>
+    <definedName name="solver_rhs2" localSheetId="2" hidden="1">0.3</definedName>
+    <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="2" hidden="1">3</definedName>
+    <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="75">
   <si>
     <t>Act prim</t>
   </si>
@@ -209,381 +210,6 @@
     <t>insumo-producto-actividad</t>
   </si>
   <si>
-    <t>fit                                  0.150</t>
-  </si>
-  <si>
-    <t>k_total_data                        54.113</t>
-  </si>
-  <si>
-    <t>l_total_data                        34.133</t>
-  </si>
-  <si>
-    <t>omega                                2.000</t>
-  </si>
-  <si>
-    <t>par_k_h                              0.223</t>
-  </si>
-  <si>
-    <t>par_k_f                              0.575</t>
-  </si>
-  <si>
-    <t>par_k_row                            0.184</t>
-  </si>
-  <si>
-    <t>par_k_g                              0.018</t>
-  </si>
-  <si>
-    <t>pit                                  0.017</t>
-  </si>
-  <si>
-    <t>por_l_h                              1.000</t>
-  </si>
-  <si>
-    <t>por_sav                              0.076</t>
-  </si>
-  <si>
-    <t>por_cont                             0.105</t>
-  </si>
-  <si>
-    <t>por_tremp                            0.245</t>
-  </si>
-  <si>
-    <t>por_trgov                            0.030</t>
-  </si>
-  <si>
-    <t>por_prest                            0.077</t>
-  </si>
-  <si>
-    <t>por_sav_f                            0.361</t>
-  </si>
-  <si>
-    <t>por_cont_soc_f                       0.783</t>
-  </si>
-  <si>
-    <t>por_l_row                            0.000</t>
-  </si>
-  <si>
-    <t>por_cont_soc_g                       0.217</t>
-  </si>
-  <si>
-    <t>por_sav_g                            0.120</t>
-  </si>
-  <si>
-    <t>alpha__Prodprim                      0.200</t>
-  </si>
-  <si>
-    <t>alpha__Prodmanu                      0.200</t>
-  </si>
-  <si>
-    <t>alpha__Prodserv                      0.200</t>
-  </si>
-  <si>
-    <t>aran__Prodprim                       0.014</t>
-  </si>
-  <si>
-    <t>aran__Prodmanu                       0.018</t>
-  </si>
-  <si>
-    <t>aran__Prodserv                       0.000</t>
-  </si>
-  <si>
-    <t>beta_k__Prodprim__Actprim            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodprim__Actmanu            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodprim__Actserv            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodmanu__Actprim            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodmanu__Actmanu            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodmanu__Actserv            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodserv__Actprim            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodserv__Actmanu            0.600</t>
-  </si>
-  <si>
-    <t>beta_k__Prodserv__Actserv            0.600</t>
-  </si>
-  <si>
-    <t>beta_l__Prodprim__Actprim            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodprim__Actmanu            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodprim__Actserv            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodmanu__Actprim            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodmanu__Actmanu            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodmanu__Actserv            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodserv__Actprim            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodserv__Actmanu            0.400</t>
-  </si>
-  <si>
-    <t>beta_l__Prodserv__Actserv            0.400</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodprim__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodprim__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodprim__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodmanu__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodmanu__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodmanu__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodserv__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodserv__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodprim__Prodserv__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodprim__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodprim__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodprim__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodmanu__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodmanu__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodmanu__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodserv__Actprim  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodserv__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodmanu__Prodserv__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodprim__Actprim  0.050</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodprim__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodprim__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodmanu__Actprim  0.050</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodmanu__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodmanu__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodserv__Actprim  0.050</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodserv__Actmanu  0.250</t>
-  </si>
-  <si>
-    <t>beta_x__Prodserv__Prodserv__Actserv  0.250</t>
-  </si>
-  <si>
-    <t>d_data__Prodmanu                    23.090</t>
-  </si>
-  <si>
-    <t>d_data__Prodserv                    32.838</t>
-  </si>
-  <si>
-    <t>gamma__Prodprim__Actprim             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodprim__Actmanu             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodprim__Actserv             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodmanu__Actprim             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodmanu__Actmanu             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodmanu__Actserv             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodserv__Actprim             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodserv__Actmanu             0.150</t>
-  </si>
-  <si>
-    <t>gamma__Prodserv__Actserv             0.150</t>
-  </si>
-  <si>
-    <t>l_data__Actprim                      2.988</t>
-  </si>
-  <si>
-    <t>l_data__Actmanu                      7.101</t>
-  </si>
-  <si>
-    <t>l_data__Actserv                     24.044</t>
-  </si>
-  <si>
-    <t>por_m__Prodprim                      0.165</t>
-  </si>
-  <si>
-    <t>por_m__Prodmanu                      0.290</t>
-  </si>
-  <si>
-    <t>por_m__Prodserv                      0.048</t>
-  </si>
-  <si>
-    <t>por_x__Prodprim                      0.525</t>
-  </si>
-  <si>
-    <t>por_x__Prodmanu                      0.138</t>
-  </si>
-  <si>
-    <t>por_x__Prodserv                      0.075</t>
-  </si>
-  <si>
-    <t>por_gg_p__Prodprim                   0.000</t>
-  </si>
-  <si>
-    <t>por_gg_p__Prodmanu                   0.001</t>
-  </si>
-  <si>
-    <t>por_gg_p__Prodserv                   0.110</t>
-  </si>
-  <si>
-    <t>t_prod__Actprim                      0.004</t>
-  </si>
-  <si>
-    <t>t_prod__Actmanu                      0.019</t>
-  </si>
-  <si>
-    <t>t_prod__Actserv                      0.030</t>
-  </si>
-  <si>
-    <t>vat__Prodprim                        0.007</t>
-  </si>
-  <si>
-    <t>vat__Prodmanu                        0.054</t>
-  </si>
-  <si>
-    <t>vat__Prodserv                        0.006</t>
-  </si>
-  <si>
-    <t>x_data__Prodprim__Actprim            3.160</t>
-  </si>
-  <si>
-    <t>x_data__Prodprim__Actmanu           11.928</t>
-  </si>
-  <si>
-    <t>x_data__Prodprim__Actserv            0.164</t>
-  </si>
-  <si>
-    <t>x_data__Prodmanu__Actprim            6.914</t>
-  </si>
-  <si>
-    <t>x_data__Prodmanu__Actmanu           22.115</t>
-  </si>
-  <si>
-    <t>x_data__Prodmanu__Actserv           11.397</t>
-  </si>
-  <si>
-    <t>x_data__Prodserv__Actprim            4.446</t>
-  </si>
-  <si>
-    <t>x_data__Prodserv__Actmanu           10.255</t>
-  </si>
-  <si>
-    <t>x_data__Prodserv__Actserv           25.790</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>este podría ser sobre los ingresos de las empresas</t>
-  </si>
-  <si>
-    <t>este podría ser sobre los ingresos del gobierno</t>
-  </si>
-  <si>
-    <t>podria ser a partir del del gob y las firmas</t>
-  </si>
-  <si>
-    <t>por_pres_soc_g                       0.723</t>
-  </si>
-  <si>
-    <t>por_pres_soc_f                       0.277</t>
-  </si>
-  <si>
-    <t>este % es sobre el total</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actprim__Prodprim      28.803</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actprim__Prodmanu       1.070</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actprim__Prodserv       0.942</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actmanu__Prodprim       0.174</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actmanu__Prodmanu      62.724</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actmanu__Prodserv       1.318</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actserv__Prodprim       0.000</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actserv__Prodmanu       1.495</t>
-  </si>
-  <si>
-    <t>data_prod_s__Actserv__Prodserv      87.052</t>
-  </si>
-  <si>
     <t>L prim</t>
   </si>
   <si>
@@ -667,15 +293,22 @@
   <si>
     <t>tasa vat</t>
   </si>
+  <si>
+    <t>Esta el la base de las SAMs que se están utilizando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pasar el arancel al IVA </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0000000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -796,7 +429,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
@@ -1171,7 +805,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1180,11 +814,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1231,7 +867,7 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
     <dxf>
       <fill>
         <patternFill>
@@ -1398,6 +1034,23 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1676,78 +1329,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9002378-D1AE-4036-8BAA-A66B6A430E56}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:Y59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.15">
       <c r="B1" s="1" t="s">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5">
         <v>0</v>
       </c>
       <c r="C2" s="5">
-        <v>83.492336422509979</v>
+        <v>0</v>
       </c>
       <c r="D2" s="5">
         <v>0</v>
       </c>
       <c r="E2" s="5">
-        <v>0</v>
+        <v>28.688309060889999</v>
       </c>
       <c r="F2" s="5">
-        <v>0</v>
+        <v>1.069724034</v>
       </c>
       <c r="G2" s="5">
-        <v>0</v>
+        <v>0.94155019620000002</v>
       </c>
       <c r="H2" s="5">
         <v>0</v>
@@ -1768,22 +1450,49 @@
         <v>0</v>
       </c>
       <c r="N2" s="5">
-        <f t="shared" ref="N2:N13" si="0">+SUM(B2:M2)</f>
-        <v>83.492336422509979</v>
-      </c>
-      <c r="O2" t="s">
-        <v>177</v>
-      </c>
-      <c r="Q2" s="7">
-        <f>+SUM(C2:C2)</f>
-        <v>83.492336422509979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>0</v>
+      </c>
+      <c r="R2" s="5">
+        <v>0</v>
+      </c>
+      <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
+        <v>0</v>
+      </c>
+      <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
+        <v>0</v>
+      </c>
+      <c r="W2" s="5">
+        <f>+SUM(B2:V2)</f>
+        <v>30.699583291090001</v>
+      </c>
+      <c r="X2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y2" s="7">
+        <f>+U2+V2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5">
         <v>0</v>
       </c>
       <c r="C3" s="5">
@@ -1793,16 +1502,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="5">
-        <v>0</v>
+        <v>0.17356569899999999</v>
       </c>
       <c r="F3" s="5">
-        <v>56.02172243576166</v>
+        <v>61.503785585719996</v>
       </c>
       <c r="G3" s="5">
-        <v>0</v>
+        <v>1.318426093</v>
       </c>
       <c r="H3" s="5">
-        <v>10.495365456630001</v>
+        <v>0</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
@@ -1817,1019 +1526,2056 @@
         <v>0</v>
       </c>
       <c r="M3" s="5">
-        <v>24.362225892369995</v>
+        <v>0</v>
       </c>
       <c r="N3" s="5">
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>0</v>
+      </c>
+      <c r="U3" s="5">
+        <v>0</v>
+      </c>
+      <c r="V3" s="5">
+        <v>0</v>
+      </c>
+      <c r="W3" s="5">
+        <f t="shared" ref="W3:W22" si="0">+SUM(B3:V3)</f>
+        <v>62.995777377719996</v>
+      </c>
+      <c r="X3" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y3" s="7">
+        <f t="shared" ref="Y3:Y22" si="1">+U3+V3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1.495441644</v>
+      </c>
+      <c r="G4" s="5">
+        <v>84.471346864999987</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
         <f t="shared" si="0"/>
-        <v>90.879313784761649</v>
-      </c>
-      <c r="P3" s="7"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
+        <v>85.966788508999983</v>
+      </c>
+      <c r="Y4" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5">
+        <v>3.1605375580000001</v>
+      </c>
+      <c r="C5" s="5">
+        <v>11.927984220000001</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0.16408898730000002</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>13.773547216400001</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1.75329745E-2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0.16482158305</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5">
+        <f t="shared" si="0"/>
+        <v>29.208512539250002</v>
+      </c>
+      <c r="Y5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.16482158305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5">
+        <v>6.9137747879999996</v>
+      </c>
+      <c r="C6" s="5">
+        <v>22.11542081</v>
+      </c>
+      <c r="D6" s="5">
+        <v>11.39658985</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>8.4945261772000027</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>8.3720262130000001E-2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>20.612622200999997</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5">
+        <f t="shared" si="0"/>
+        <v>69.616654088329994</v>
+      </c>
+      <c r="Y6" s="7">
+        <f t="shared" si="1"/>
+        <v>20.612622200999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5">
+        <v>4.4456911320000003</v>
+      </c>
+      <c r="C7" s="5">
+        <v>10.25533388</v>
+      </c>
+      <c r="D7" s="5">
+        <v>25.790391530000001</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>34.326412584000003</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>10.39411222</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>3.5847821083199998</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5">
+        <f t="shared" si="0"/>
+        <v>88.796723454320002</v>
+      </c>
+      <c r="Y7" s="7">
+        <f t="shared" si="1"/>
+        <v>3.5847821083199998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
-        <v>34.133031362509982</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-      <c r="N4" s="5">
+      <c r="B8" s="5">
+        <v>2.9878268870000002</v>
+      </c>
+      <c r="C8" s="5">
+        <v>7.1010807900000001</v>
+      </c>
+      <c r="D8" s="5">
+        <v>24.0441237</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
         <f t="shared" si="0"/>
-        <v>34.133031362509982</v>
-      </c>
-      <c r="Q4" s="7">
-        <f>+SUM(B4:B4)</f>
-        <v>34.133031362509982</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
+        <v>34.133031377000002</v>
+      </c>
+      <c r="Y8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="5">
-        <v>49.359305059999997</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5">
-        <v>0</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-      <c r="N5" s="5">
+      <c r="B9" s="5">
+        <v>13.19175293</v>
+      </c>
+      <c r="C9" s="5">
+        <v>11.59595768</v>
+      </c>
+      <c r="D9" s="5">
+        <v>24.571594449999999</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
+      <c r="R9" s="5">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
+        <v>0</v>
+      </c>
+      <c r="U9" s="5">
+        <v>0</v>
+      </c>
+      <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
         <f t="shared" si="0"/>
         <v>49.359305059999997</v>
       </c>
-      <c r="Q5" s="7">
-        <f>+SUM(B5:B5)</f>
-        <v>49.359305059999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A6" s="1" t="s">
+      <c r="Y9" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="5">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
         <v>34.133031370000005</v>
       </c>
-      <c r="E6" s="5">
+      <c r="I10" s="5">
         <v>17.281502200000006</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
         <v>17.431284399999999</v>
       </c>
-      <c r="H6" s="5">
-        <v>0.55637803610000003</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <f>4.0619130575+0.0272368961616536</f>
-        <v>4.0891499536616536</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-      <c r="N6" s="5">
+      <c r="L10" s="5">
+        <v>2.1073795340000001</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>3.11076672</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
         <f t="shared" si="0"/>
-        <v>73.491345959761674</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A7" s="1" t="s">
+        <v>74.063964224000017</v>
+      </c>
+      <c r="Y10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
         <v>31.096709390000001</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
         <v>5.8570051300000001</v>
       </c>
-      <c r="J7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <v>0</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0</v>
-      </c>
-      <c r="M7" s="5">
-        <v>0</v>
-      </c>
-      <c r="N7" s="5">
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="5">
+        <v>0</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
+        <v>0</v>
+      </c>
+      <c r="W11" s="5">
         <f t="shared" si="0"/>
         <v>36.953714519999998</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A8" s="1" t="s">
+      <c r="Y11" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="5">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
         <v>0.98109349999999995</v>
       </c>
-      <c r="F8" s="5">
-        <v>0</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
         <v>1.6238783000000001</v>
       </c>
-      <c r="J8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5">
         <v>5.8828657</v>
       </c>
-      <c r="L8" s="5">
-        <v>7.3869768860000002</v>
-      </c>
-      <c r="M8" s="5">
-        <v>0</v>
-      </c>
-      <c r="N8" s="5">
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5">
+        <v>7.9597404277999999</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
         <f t="shared" si="0"/>
-        <v>15.874814386000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A9" s="1" t="s">
+        <v>16.447577927799998</v>
+      </c>
+      <c r="Y12" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
         <v>7.4808834299999996</v>
       </c>
-      <c r="G9" s="5">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0</v>
-      </c>
-      <c r="M9" s="5">
-        <v>0</v>
-      </c>
-      <c r="N9" s="5">
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
+      <c r="R13" s="5">
+        <v>0</v>
+      </c>
+      <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5">
         <f t="shared" si="0"/>
         <v>7.4808834299999996</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A10" s="1" t="s">
+      <c r="Y13" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="5">
-        <v>0</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0</v>
-      </c>
-      <c r="E10" s="5">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="B14" s="5">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
         <v>1.5233916200000002</v>
       </c>
-      <c r="H10" s="5">
-        <f>2.5385214375+0.0272368961616536</f>
-        <v>2.5657583336616536</v>
-      </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5">
-        <v>0</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0</v>
-      </c>
-      <c r="M10" s="5">
-        <v>0</v>
-      </c>
-      <c r="N10" s="5">
+      <c r="L14" s="5">
+        <v>1.5873751</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
+      <c r="R14" s="5">
+        <v>0</v>
+      </c>
+      <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
+        <v>0</v>
+      </c>
+      <c r="U14" s="5">
+        <v>0</v>
+      </c>
+      <c r="V14" s="5">
+        <v>0</v>
+      </c>
+      <c r="W14" s="5">
         <f t="shared" si="0"/>
-        <v>4.0891499536616536</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A11" s="1" t="s">
+        <v>3.11076672</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5">
-        <v>0</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="E11" s="5">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5">
+      <c r="B15" s="5">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
         <v>1.2089669999999999</v>
       </c>
-      <c r="G11" s="5">
+      <c r="K15" s="5">
         <v>4.6738986999999996</v>
       </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
+      <c r="R15" s="5">
+        <v>0</v>
+      </c>
+      <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5">
         <f t="shared" si="0"/>
         <v>5.8828657</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A12" s="1" t="s">
+      <c r="Y15" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
+      <c r="R16" s="5">
+        <v>0</v>
+      </c>
+      <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
+        <v>0</v>
+      </c>
+      <c r="U16" s="5">
+        <v>0</v>
+      </c>
+      <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y16" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="5">
-        <v>0</v>
-      </c>
-      <c r="C12" s="5">
-        <v>7.3869768858900002</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="E12" s="5">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5">
-        <v>0</v>
-      </c>
-      <c r="N12" s="5">
+      <c r="B18" s="5">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.34663777383</v>
+      </c>
+      <c r="F18" s="5">
+        <v>5.5477028223799998</v>
+      </c>
+      <c r="G18" s="5">
+        <v>2.0653998315183499</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0</v>
+      </c>
+      <c r="M18" s="5">
+        <v>0</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
+      <c r="R18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
+        <v>0</v>
+      </c>
+      <c r="T18" s="5">
+        <v>0</v>
+      </c>
+      <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
+        <v>0</v>
+      </c>
+      <c r="W18" s="5">
         <f t="shared" si="0"/>
-        <v>7.3869768858900002</v>
-      </c>
-      <c r="Q12" s="7">
-        <f>+SUM(C12:C12)</f>
-        <v>7.3869768858900002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+        <v>7.9597404277283506</v>
+      </c>
+      <c r="Y18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0</v>
+      </c>
+      <c r="M19" s="5">
+        <v>0</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
+      <c r="R19" s="5">
+        <v>0</v>
+      </c>
+      <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
+      <c r="R20" s="5">
+        <v>0</v>
+      </c>
+      <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
+        <v>0</v>
+      </c>
+      <c r="U20" s="5">
+        <v>0</v>
+      </c>
+      <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="5">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>0</v>
-      </c>
-      <c r="E13" s="5">
-        <v>0</v>
-      </c>
-      <c r="F13" s="5">
+      <c r="B21" s="5">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5">
+        <v>0</v>
+      </c>
+      <c r="H21" s="5">
+        <v>0</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
         <v>8.7797730940000012</v>
       </c>
-      <c r="G13" s="5">
+      <c r="K21" s="5">
         <v>13.325139800000001</v>
       </c>
-      <c r="H13" s="5">
+      <c r="L21" s="5">
         <v>2.2573129999999999</v>
       </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="5">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5">
-        <v>0</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0</v>
-      </c>
-      <c r="M13" s="5">
-        <v>0</v>
-      </c>
-      <c r="N13" s="5">
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5">
+        <v>0</v>
+      </c>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
+      <c r="R21" s="5">
+        <v>0</v>
+      </c>
+      <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
+        <v>0</v>
+      </c>
+      <c r="U21" s="5">
+        <v>0</v>
+      </c>
+      <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
         <f t="shared" si="0"/>
         <v>24.362225894000002</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="Y21" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
+      <c r="R22" s="5">
+        <v>0</v>
+      </c>
+      <c r="S22" s="5">
+        <v>0</v>
+      </c>
+      <c r="T22" s="5">
+        <v>0</v>
+      </c>
+      <c r="U22" s="5">
+        <v>0</v>
+      </c>
+      <c r="V22" s="5">
+        <v>0</v>
+      </c>
+      <c r="W22" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Y22" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5">
-        <f t="shared" ref="B14:M14" si="1">+SUM(B2:B13)</f>
-        <v>83.492336422509979</v>
-      </c>
-      <c r="C14" s="5">
-        <f t="shared" si="1"/>
-        <v>90.879313308399986</v>
-      </c>
-      <c r="D14" s="5">
-        <f t="shared" si="1"/>
+      <c r="B23" s="5">
+        <f>+SUM(B2:B22)</f>
+        <v>30.699583295</v>
+      </c>
+      <c r="C23" s="5">
+        <f t="shared" ref="C23:V23" si="2">+SUM(C2:C22)</f>
+        <v>62.99577738</v>
+      </c>
+      <c r="D23" s="5">
+        <f t="shared" si="2"/>
+        <v>85.966788517299989</v>
+      </c>
+      <c r="E23" s="5">
+        <f t="shared" si="2"/>
+        <v>29.20851253372</v>
+      </c>
+      <c r="F23" s="5">
+        <f t="shared" si="2"/>
+        <v>69.616654086099999</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="2"/>
+        <v>88.796722985718333</v>
+      </c>
+      <c r="H23" s="5">
+        <f t="shared" si="2"/>
         <v>34.133031370000005</v>
       </c>
-      <c r="E14" s="5">
-        <f t="shared" si="1"/>
+      <c r="I23" s="5">
+        <f t="shared" si="2"/>
         <v>49.359305090000007</v>
       </c>
-      <c r="F14" s="5">
-        <f t="shared" si="1"/>
-        <v>73.491345959761659</v>
-      </c>
-      <c r="G14" s="5">
-        <f t="shared" si="1"/>
+      <c r="J23" s="5">
+        <f t="shared" si="2"/>
+        <v>74.064109501600015</v>
+      </c>
+      <c r="K23" s="5">
+        <f t="shared" si="2"/>
         <v>36.953714519999998</v>
       </c>
-      <c r="H14" s="5">
-        <f t="shared" si="1"/>
-        <v>15.874814826391654</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="1"/>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>16.44743309063</v>
+      </c>
+      <c r="M23" s="5">
+        <f t="shared" si="2"/>
         <v>7.4808834300000004</v>
       </c>
-      <c r="J14" s="5">
-        <f t="shared" si="1"/>
-        <v>4.0891499536616536</v>
-      </c>
-      <c r="K14" s="5">
-        <f t="shared" si="1"/>
+      <c r="N23" s="5">
+        <f t="shared" si="2"/>
+        <v>3.11076672</v>
+      </c>
+      <c r="O23" s="5">
+        <f t="shared" si="2"/>
         <v>5.8828657</v>
       </c>
-      <c r="L14" s="5">
-        <f t="shared" si="1"/>
-        <v>7.3869768860000002</v>
-      </c>
-      <c r="M14" s="5">
-        <f t="shared" si="1"/>
+      <c r="P23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="5">
+        <f t="shared" si="2"/>
+        <v>7.9597404277999999</v>
+      </c>
+      <c r="S23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U23" s="5">
+        <f t="shared" si="2"/>
         <v>24.362225892369995</v>
       </c>
-      <c r="N14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="B16">
-        <f t="array" ref="B16:M16">TRANSPOSE(N2:N13)</f>
-        <v>83.492336422509979</v>
-      </c>
-      <c r="C16">
-        <v>90.879313784761649</v>
-      </c>
-      <c r="D16">
-        <v>34.133031362509982</v>
-      </c>
-      <c r="E16">
+      <c r="V23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <f t="array" ref="B25:V25">TRANSPOSE(W2:W22)</f>
+        <v>30.699583291090001</v>
+      </c>
+      <c r="C25">
+        <v>62.995777377719996</v>
+      </c>
+      <c r="D25">
+        <v>85.966788508999983</v>
+      </c>
+      <c r="E25">
+        <v>29.208512539250002</v>
+      </c>
+      <c r="F25">
+        <v>69.616654088329994</v>
+      </c>
+      <c r="G25">
+        <v>88.796723454320002</v>
+      </c>
+      <c r="H25">
+        <v>34.133031377000002</v>
+      </c>
+      <c r="I25">
         <v>49.359305059999997</v>
       </c>
-      <c r="F16">
-        <v>73.491345959761674</v>
-      </c>
-      <c r="G16">
+      <c r="J25">
+        <v>74.063964224000017</v>
+      </c>
+      <c r="K25">
         <v>36.953714519999998</v>
       </c>
-      <c r="H16">
-        <v>15.874814386000001</v>
-      </c>
-      <c r="I16">
+      <c r="L25">
+        <v>16.447577927799998</v>
+      </c>
+      <c r="M25">
         <v>7.4808834299999996</v>
       </c>
-      <c r="J16">
-        <v>4.0891499536616536</v>
-      </c>
-      <c r="K16">
+      <c r="N25">
+        <v>3.11076672</v>
+      </c>
+      <c r="O25">
         <v>5.8828657</v>
       </c>
-      <c r="L16">
-        <v>7.3869768858900002</v>
-      </c>
-      <c r="M16">
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>7.9597404277283506</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
         <v>24.362225894000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B17" s="12">
-        <f>+B14-B16</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="12">
-        <f t="shared" ref="C17:M17" si="2">+C14-C16</f>
-        <v>-4.7636166300435434E-7</v>
-      </c>
-      <c r="D17" s="12">
-        <f t="shared" si="2"/>
-        <v>7.4900228241858713E-9</v>
-      </c>
-      <c r="E17" s="12">
-        <f t="shared" si="2"/>
-        <v>3.0000009587638488E-8</v>
-      </c>
-      <c r="F17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="12">
-        <f t="shared" si="2"/>
-        <v>4.4039165381093426E-7</v>
-      </c>
-      <c r="I17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="12">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
-        <f t="shared" si="2"/>
-        <v>1.1000000910144081E-10</v>
-      </c>
-      <c r="M17" s="12">
-        <f t="shared" si="2"/>
-        <v>-1.6300063521157426E-9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B18" s="2">
-        <f>ROUND(B14-B16,1)</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="2">
-        <f t="shared" ref="C18:M18" si="3">ROUND(C14-C16,1)</f>
-        <v>0</v>
-      </c>
-      <c r="D18" s="2">
+      <c r="V25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="E26" s="7">
+        <f>+E25-E23</f>
+        <v>5.5300013457326713E-9</v>
+      </c>
+      <c r="F26" s="7">
+        <f t="shared" ref="F26:G26" si="3">+F25-F23</f>
+        <v>2.2299957436189288E-9</v>
+      </c>
+      <c r="G26" s="7">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="G18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="5">
-        <v>12733.68651</v>
-      </c>
-      <c r="F20" s="7">
-        <f>+SUM(F3:F3)</f>
-        <v>56.02172243576166</v>
-      </c>
-      <c r="H20" s="7">
-        <f>+SUM(H3:H3)</f>
-        <v>10.495365456630001</v>
-      </c>
-      <c r="M20" s="7">
-        <f>+SUM(M3:M3)</f>
-        <v>24.362225892369995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A22" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="J22" s="7">
-        <f>+J6-C39</f>
-        <v>4.0891499536616536</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="F23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="J23" s="7">
-        <f>+H10-C39</f>
-        <v>2.5657583336616536</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B25">
-        <v>1000000</v>
-      </c>
-      <c r="F25">
-        <v>2.723689616165359E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="E26" s="7"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B27" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B28" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B29" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B30" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="B31" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B33" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B35" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+        <v>4.6860166946771642E-7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B27" s="14">
+        <f>ROUND(B23-B25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="14">
+        <f>ROUND(C23-C25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <f>ROUND(D23-D25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="14">
+        <f>ROUND(E23-E25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <f>ROUND(F23-F25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <f>ROUND(G23-G25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <f t="shared" ref="H27:V27" si="4">ROUND(H23-H25,3)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B28" s="7">
+        <f>+B23-B25</f>
+        <v>3.9099994353364309E-9</v>
+      </c>
+      <c r="C28" s="7">
+        <f t="shared" ref="C28:D28" si="5">+C23-C25</f>
+        <v>2.2800037413617247E-9</v>
+      </c>
+      <c r="D28" s="7">
+        <f t="shared" si="5"/>
+        <v>8.3000060158155975E-9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B29" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" ref="H29:I29" si="6">+H20+H10</f>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="I29" s="7">
+        <f>+I20+I10</f>
+        <v>17.281502200000006</v>
+      </c>
+      <c r="J29" s="7">
+        <f>+J21+T21</f>
+        <v>8.7797730940000012</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="7">
+        <f>+I29-T9</f>
+        <v>17.281502200000006</v>
+      </c>
+      <c r="Q30" s="7">
+        <f>+L10-P12-Q12</f>
+        <v>2.1073795340000001</v>
+      </c>
+      <c r="R30" s="7">
+        <f>+R12+S12</f>
+        <v>7.9597404277999999</v>
+      </c>
+      <c r="S30" s="7">
+        <f>+L10-S12</f>
+        <v>2.1073795340000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B31" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="U31" s="7">
+        <f>+U5+V5</f>
+        <v>0.16482158305</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.15">
+      <c r="B32" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32">
+        <v>-2.3959999999999999</v>
+      </c>
+      <c r="U32" s="7">
+        <f t="shared" ref="U32:U33" si="7">+U6+V6</f>
+        <v>20.612622200999997</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B33" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="U33" s="7">
+        <f t="shared" si="7"/>
+        <v>3.5847821083199998</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B34" s="13"/>
+      <c r="J34" s="7">
+        <f>+N10+J32</f>
+        <v>0.71476672000000008</v>
+      </c>
+      <c r="K34" s="7">
+        <f>+L14+J32</f>
+        <v>-0.80862489999999987</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B35" s="11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B42" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B43" s="5">
-        <v>3.1605375580000001</v>
-      </c>
-      <c r="D43" s="7" t="e">
-        <f>+#REF!-B47</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F43" s="7" t="e">
-        <f>+F3+D43</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A44" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B44" s="5">
-        <v>6.9137747879999996</v>
-      </c>
-      <c r="D44" s="7" t="e">
-        <f>+#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7" t="e">
-        <f>+#REF!+D44</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="5">
-        <v>4.4456911320000003</v>
-      </c>
-      <c r="D45" s="7" t="e">
-        <f>+#REF!-#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F45" s="7" t="e">
-        <f>+#REF!+D45</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B43" s="7">
+        <f>+J5+T5</f>
+        <v>13.773547216400001</v>
+      </c>
+      <c r="C43" s="7">
+        <f>+B43-E20</f>
+        <v>13.773547216400001</v>
+      </c>
+      <c r="D43" s="7">
+        <f>+C43-E19</f>
+        <v>13.773547216400001</v>
+      </c>
+      <c r="E43" s="7">
+        <f>+D43-B16-B17</f>
+        <v>13.773547216400001</v>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7">
+        <f>+I10-T9</f>
+        <v>17.281502200000006</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B44" s="7">
+        <f t="shared" ref="B44:B45" si="8">+J6+T6</f>
+        <v>8.4945261772000027</v>
+      </c>
+      <c r="C44" s="7">
+        <f>+B44-F20</f>
+        <v>8.4945261772000027</v>
+      </c>
+      <c r="D44" s="7">
+        <f>+C44-F19</f>
+        <v>8.4945261772000027</v>
+      </c>
+      <c r="E44" s="7">
+        <f>+D44-C16-C17</f>
+        <v>8.4945261772000027</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="B45" s="7">
+        <f t="shared" si="8"/>
+        <v>34.326412584000003</v>
+      </c>
+      <c r="C45" s="7">
+        <f>+B45-G20</f>
+        <v>34.326412584000003</v>
+      </c>
+      <c r="D45" s="7">
+        <f>+C45-G19</f>
+        <v>34.326412584000003</v>
+      </c>
+      <c r="E45" s="7">
+        <f>+D45-D16-D17</f>
+        <v>34.326412584000003</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.15">
       <c r="B47" s="7">
-        <f>+SUM(B43:B45)</f>
-        <v>14.520003478</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="B49" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="B51" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="B52" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" s="5">
-        <v>14.16830558289</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A54" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B54" s="5">
-        <v>0.17356569899999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B55" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="B57" s="7">
-        <f>+SUM(B53:B55)</f>
-        <v>14.341871281889999</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+        <f>+H10+H20</f>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="C47" s="7">
+        <f>+I10+I20</f>
+        <v>17.281502200000006</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.15">
+      <c r="E48" s="7">
+        <f>+E18+E19</f>
+        <v>0.34663777383</v>
+      </c>
+      <c r="F48" s="7">
+        <f t="shared" ref="F48:G48" si="9">+F18+F19</f>
+        <v>5.5477028223799998</v>
+      </c>
+      <c r="G48" s="7">
+        <f t="shared" si="9"/>
+        <v>2.0653998315183499</v>
+      </c>
+      <c r="I48" s="7">
+        <f>+L14-G48</f>
+        <v>-0.4780247315183499</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B49" s="7">
+        <f>+J21+T21</f>
+        <v>8.7797730940000012</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="7">
+        <f>+B16+B17</f>
+        <v>0</v>
+      </c>
+      <c r="C51" s="7">
+        <f t="shared" ref="C51:D51" si="10">+C16+C17</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B53">
+        <f>+macro_sam_2008_v1!B16</f>
+        <v>0.10199653260000001</v>
+      </c>
+      <c r="C53">
+        <f>+macro_sam_2008_v1!C16</f>
+        <v>0.2486144549</v>
+      </c>
+      <c r="D53">
+        <f>+macro_sam_2008_v1!D16</f>
+        <v>1.0942426750000001</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54">
+        <f>+macro_sam_2008_v1!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <f>+macro_sam_2008_v1!C17</f>
+        <v>0.95100149789999999</v>
+      </c>
+      <c r="D54">
+        <f>+macro_sam_2008_v1!D17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B56">
+        <f>+B53+B54</f>
+        <v>0.10199653260000001</v>
+      </c>
+      <c r="C56">
+        <f t="shared" ref="C56:D56" si="11">+C53+C54</f>
+        <v>1.1996159527999999</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="11"/>
+        <v>1.0942426750000001</v>
+      </c>
+      <c r="F56">
+        <f>+SUM(B56:D56)</f>
+        <v>2.3958551604</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="7">
+        <f>+E2-B16</f>
+        <v>28.688309060889999</v>
+      </c>
+      <c r="C58" s="7">
+        <f>+F3-C16-C17</f>
+        <v>61.503785585719996</v>
+      </c>
+      <c r="D58" s="7">
+        <f>+G4-D16</f>
+        <v>84.471346864999987</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="7">
-        <v>1.8377085351100018</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="A60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="5">
-        <v>2.9878268870000002</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
-      <c r="B62" s="7">
-        <f>+B60-B59</f>
-        <v>1.1501183518899984</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A65" s="7" t="str">
-        <f>+A4</f>
-        <v>Trabajo</v>
-      </c>
-      <c r="B65" s="7">
-        <f>+B4</f>
-        <v>34.133031362509982</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A66" s="7" t="str">
-        <f>+A5</f>
-        <v>Capital</v>
-      </c>
-      <c r="B66" s="7">
-        <f>+B5</f>
-        <v>49.359305059999997</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A67" s="7" t="str">
-        <f>+A14</f>
-        <v>Total</v>
-      </c>
-      <c r="B67" s="7">
-        <f>+B14</f>
-        <v>83.492336422509979</v>
-      </c>
-      <c r="D67">
-        <f>B70*(B65^B69)*(B66^(1-B69))</f>
-        <v>83.492336422509979</v>
-      </c>
-      <c r="F67" s="7">
-        <f>+B67-D67</f>
-        <v>0</v>
-      </c>
-      <c r="H67">
-        <f>(B65^B69)*(B66^D69)</f>
-        <v>41.746166797763046</v>
-      </c>
-      <c r="J67">
-        <f>+B67/H67</f>
-        <v>2.0000000677184064</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A69" t="s">
-        <v>195</v>
-      </c>
-      <c r="B69">
-        <v>0.45415154287117893</v>
-      </c>
-      <c r="D69">
-        <f>1-B69</f>
-        <v>0.54584845712882113</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A70" t="s">
-        <v>196</v>
-      </c>
-      <c r="B70">
-        <f>+J67</f>
-        <v>2.0000000677184064</v>
-      </c>
-      <c r="F70">
-        <f>+B70*B69*(B66^D69)*(B65^(B69-1))</f>
-        <v>1.1108938143082672</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="F71">
-        <f>+D69*B70*(B66^(D69-1))*(B65^B69)</f>
-        <v>0.92331451917543572</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A75" t="s">
-        <v>197</v>
-      </c>
-      <c r="B75">
-        <v>8.7999999999999995E-2</v>
-      </c>
-      <c r="D75">
-        <f>7.5+8.8+56</f>
-        <v>72.3</v>
+        <f>+J5-B56</f>
+        <v>13.671550683800001</v>
+      </c>
+      <c r="C59" s="7">
+        <f>+J6-C56</f>
+        <v>7.2949102244000024</v>
+      </c>
+      <c r="D59" s="7">
+        <f>+J7-D56</f>
+        <v>33.232169909000007</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B20">
-    <cfRule type="cellIs" dxfId="21" priority="4" operator="notEqual">
+  <conditionalFormatting sqref="B27:V27">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B45">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B53:B55">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B60">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="notEqual">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B18:M18">
-    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:N14">
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="notEqual">
+  <conditionalFormatting sqref="B2:W23">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2935,10 +3681,10 @@
       <c r="E2" s="5">
         <v>14.341871281889999</v>
       </c>
-      <c r="F2" s="11">
-        <v>0</v>
-      </c>
-      <c r="G2" s="11">
+      <c r="F2" s="9">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9">
         <v>0</v>
       </c>
       <c r="H2" s="5">
@@ -2991,7 +3737,7 @@
         <v>14.341871281889999</v>
       </c>
       <c r="X2" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -3007,13 +3753,13 @@
       <c r="D3" s="5">
         <v>0</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="9">
         <v>0</v>
       </c>
       <c r="F3" s="5">
         <v>19.770212353719991</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="9">
         <v>0</v>
       </c>
       <c r="H3" s="5">
@@ -3066,7 +3812,7 @@
         <v>19.770212353719991</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -3082,10 +3828,10 @@
       <c r="D4" s="5">
         <v>0</v>
       </c>
-      <c r="E4" s="11">
-        <v>0</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="E4" s="9">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9">
         <v>0</v>
       </c>
       <c r="G4" s="5">
@@ -3145,13 +3891,13 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11">
+      <c r="B5" s="9">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9">
         <v>0</v>
       </c>
       <c r="E5" s="5">
@@ -3203,7 +3949,7 @@
       <c r="U5" s="5">
         <v>0.16482158305</v>
       </c>
-      <c r="V5" s="11"/>
+      <c r="V5" s="9"/>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
         <v>14.60937084733</v>
@@ -3217,13 +3963,13 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="B6" s="9">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9">
         <v>0</v>
       </c>
       <c r="E6" s="5">
@@ -3275,7 +4021,7 @@
       <c r="U6" s="5">
         <v>20.612622200999997</v>
       </c>
-      <c r="V6" s="11"/>
+      <c r="V6" s="9"/>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
         <v>24.824325021429996</v>
@@ -3289,13 +4035,13 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="11">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11">
-        <v>0</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="B7" s="9">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="5">
@@ -3347,7 +4093,7 @@
       <c r="U7" s="5">
         <v>3.5847821083199998</v>
       </c>
-      <c r="V7" s="11"/>
+      <c r="V7" s="9"/>
       <c r="W7" s="5">
         <f t="shared" si="0"/>
         <v>51.445617916001666</v>
@@ -3689,12 +4435,12 @@
       <c r="O12" s="5">
         <v>5.8828657</v>
       </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
       <c r="R12" s="5">
         <v>7.3869768860000002</v>
       </c>
-      <c r="S12" s="11"/>
+      <c r="S12" s="9"/>
       <c r="T12" s="5">
         <v>0</v>
       </c>
@@ -3929,9 +4675,9 @@
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="5">
         <v>0</v>
       </c>
@@ -3998,7 +4744,7 @@
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="5">
         <v>0</v>
       </c>
@@ -4149,9 +4895,9 @@
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="5">
         <v>0</v>
       </c>
@@ -4215,11 +4961,11 @@
       <c r="D20" s="5">
         <v>0</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="5">
         <v>0</v>
       </c>
@@ -4322,7 +5068,7 @@
       <c r="S21" s="5">
         <v>0</v>
       </c>
-      <c r="T21" s="11"/>
+      <c r="T21" s="9"/>
       <c r="U21" s="5">
         <v>0</v>
       </c>
@@ -4395,7 +5141,7 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="11"/>
+      <c r="U22" s="9"/>
       <c r="V22" s="5">
         <v>0</v>
       </c>
@@ -4667,8 +5413,8 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>178</v>
+      <c r="A31" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -4697,52 +5443,52 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
-        <v>181</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
-        <v>183</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
-        <v>186</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B46" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B48" t="s">
-        <v>189</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
@@ -4854,12 +5600,12 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B58" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B60" t="s">
-        <v>191</v>
+        <v>66</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.15">
@@ -4970,32 +5716,32 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B29:D29">
-    <cfRule type="cellIs" dxfId="15" priority="4" operator="notEqual">
+    <cfRule type="cellIs" dxfId="21" priority="4" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:D54">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B62:D64">
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B69:D69">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="notEqual">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27:V27">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="6" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:W23">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="notEqual">
+    <cfRule type="cellIs" dxfId="16" priority="5" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5005,7 +5751,1176 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:Q75"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="4" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5">
+        <v>83.492336422509979</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5">
+        <v>0</v>
+      </c>
+      <c r="M2" s="5">
+        <v>0</v>
+      </c>
+      <c r="N2" s="5">
+        <f t="shared" ref="N2:N13" si="0">+SUM(B2:M2)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="O2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>+SUM(C2:C2)</f>
+        <v>83.492336422509979</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="9">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>56.02172243576166</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>10.495365456630001</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>24.362225892369995</v>
+      </c>
+      <c r="N3" s="5">
+        <f t="shared" si="0"/>
+        <v>90.879313784761649</v>
+      </c>
+      <c r="P3" s="7"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5">
+        <v>34.133031362509982</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <f t="shared" si="0"/>
+        <v>34.133031362509982</v>
+      </c>
+      <c r="Q4" s="7">
+        <f>+SUM(B4:B4)</f>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <f t="shared" si="0"/>
+        <v>49.359305059999997</v>
+      </c>
+      <c r="Q5" s="7">
+        <f>+SUM(B5:B5)</f>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>34.133031370000005</v>
+      </c>
+      <c r="E6" s="5">
+        <v>17.281502200000006</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>17.431284399999999</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.55637803610000003</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <f>4.0619130575+0.0272368961616536</f>
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <f t="shared" si="0"/>
+        <v>73.491345959761674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>31.096709390000001</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5.8570051300000001</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <f t="shared" si="0"/>
+        <v>36.953714519999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.98109349999999995</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1.6238783000000001</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>5.8828657</v>
+      </c>
+      <c r="L8" s="5">
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <f t="shared" si="0"/>
+        <v>15.874814386000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <f t="shared" si="0"/>
+        <v>7.4808834299999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1.5233916200000002</v>
+      </c>
+      <c r="H10" s="5">
+        <f>2.5385214375+0.0272368961616536</f>
+        <v>2.5657583336616536</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <f t="shared" si="0"/>
+        <v>4.0891499536616536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>1.2089669999999999</v>
+      </c>
+      <c r="G11" s="5">
+        <v>4.6738986999999996</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <f t="shared" si="0"/>
+        <v>5.8828657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <f t="shared" si="0"/>
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="Q12" s="7">
+        <f>+SUM(C12:C12)</f>
+        <v>7.3869768858900002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>8.7797730940000012</v>
+      </c>
+      <c r="G13" s="5">
+        <v>13.325139800000001</v>
+      </c>
+      <c r="H13" s="5">
+        <v>2.2573129999999999</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <f t="shared" si="0"/>
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5">
+        <f t="shared" ref="B14:M14" si="1">+SUM(B2:B13)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" si="1"/>
+        <v>90.879313308399986</v>
+      </c>
+      <c r="D14" s="5">
+        <f t="shared" si="1"/>
+        <v>34.133031370000005</v>
+      </c>
+      <c r="E14" s="5">
+        <f t="shared" si="1"/>
+        <v>49.359305090000007</v>
+      </c>
+      <c r="F14" s="5">
+        <f t="shared" si="1"/>
+        <v>73.491345959761659</v>
+      </c>
+      <c r="G14" s="5">
+        <f t="shared" si="1"/>
+        <v>36.953714519999998</v>
+      </c>
+      <c r="H14" s="5">
+        <f t="shared" si="1"/>
+        <v>15.874814826391654</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="1"/>
+        <v>7.4808834300000004</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="1"/>
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="1"/>
+        <v>5.8828657</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="1"/>
+        <v>7.3869768860000002</v>
+      </c>
+      <c r="M14" s="5">
+        <f t="shared" si="1"/>
+        <v>24.362225892369995</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+      <c r="B16">
+        <f t="array" ref="B16:M16">TRANSPOSE(N2:N13)</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="C16">
+        <v>90.879313784761649</v>
+      </c>
+      <c r="D16">
+        <v>34.133031362509982</v>
+      </c>
+      <c r="E16">
+        <v>49.359305059999997</v>
+      </c>
+      <c r="F16">
+        <v>73.491345959761674</v>
+      </c>
+      <c r="G16">
+        <v>36.953714519999998</v>
+      </c>
+      <c r="H16">
+        <v>15.874814386000001</v>
+      </c>
+      <c r="I16">
+        <v>7.4808834299999996</v>
+      </c>
+      <c r="J16">
+        <v>4.0891499536616536</v>
+      </c>
+      <c r="K16">
+        <v>5.8828657</v>
+      </c>
+      <c r="L16">
+        <v>7.3869768858900002</v>
+      </c>
+      <c r="M16">
+        <v>24.362225894000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B17" s="10">
+        <f>+B14-B16</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="10">
+        <f t="shared" ref="C17:M17" si="2">+C14-C16</f>
+        <v>-4.7636166300435434E-7</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" si="2"/>
+        <v>7.4900228241858713E-9</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" si="2"/>
+        <v>3.0000009587638488E-8</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" si="2"/>
+        <v>4.4039165381093426E-7</v>
+      </c>
+      <c r="I17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" si="2"/>
+        <v>1.1000000910144081E-10</v>
+      </c>
+      <c r="M17" s="10">
+        <f t="shared" si="2"/>
+        <v>-1.6300063521157426E-9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B18" s="2">
+        <f>ROUND(B14-B16,1)</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="2">
+        <f t="shared" ref="C18:M18" si="3">ROUND(C14-C16,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>12733.68651</v>
+      </c>
+      <c r="F20" s="7">
+        <f>+SUM(F3:F3)</f>
+        <v>56.02172243576166</v>
+      </c>
+      <c r="H20" s="7">
+        <f>+SUM(H3:H3)</f>
+        <v>10.495365456630001</v>
+      </c>
+      <c r="M20" s="7">
+        <f>+SUM(M3:M3)</f>
+        <v>24.362225892369995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="A22" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="J22" s="7">
+        <f>+J6-C39</f>
+        <v>4.0891499536616536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="F23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="J23" s="7">
+        <f>+H10-C39</f>
+        <v>2.5657583336616536</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B25">
+        <v>1000000</v>
+      </c>
+      <c r="F25">
+        <v>2.723689616165359E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B27" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B36" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="5">
+        <v>3.1605375580000001</v>
+      </c>
+      <c r="D43" s="7" t="e">
+        <f>+#REF!-B47</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F43" s="7" t="e">
+        <f>+F3+D43</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44" s="5">
+        <v>6.9137747879999996</v>
+      </c>
+      <c r="D44" s="7" t="e">
+        <f>+#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7" t="e">
+        <f>+#REF!+D44</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="5">
+        <v>4.4456911320000003</v>
+      </c>
+      <c r="D45" s="7" t="e">
+        <f>+#REF!-#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F45" s="7" t="e">
+        <f>+#REF!+D45</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="7">
+        <f>+SUM(B43:B45)</f>
+        <v>14.520003478</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B52" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B53" s="5">
+        <v>14.16830558289</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="5">
+        <v>0.17356569899999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B55" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B57" s="7">
+        <f>+SUM(B53:B55)</f>
+        <v>14.341871281889999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B59" s="7">
+        <v>1.8377085351100018</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="5">
+        <v>2.9878268870000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="B62" s="7">
+        <f>+B60-B59</f>
+        <v>1.1501183518899984</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A65" s="7" t="str">
+        <f>+A4</f>
+        <v>Trabajo</v>
+      </c>
+      <c r="B65" s="7">
+        <f>+B4</f>
+        <v>34.133031362509982</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A66" s="7" t="str">
+        <f>+A5</f>
+        <v>Capital</v>
+      </c>
+      <c r="B66" s="7">
+        <f>+B5</f>
+        <v>49.359305059999997</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A67" s="7" t="str">
+        <f>+A14</f>
+        <v>Total</v>
+      </c>
+      <c r="B67" s="7">
+        <f>+B14</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="D67">
+        <f>B70*(B65^B69)*(B66^(1-B69))</f>
+        <v>83.492336422509979</v>
+      </c>
+      <c r="F67" s="7">
+        <f>+B67-D67</f>
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <f>(B65^B69)*(B66^D69)</f>
+        <v>41.746166797763046</v>
+      </c>
+      <c r="J67">
+        <f>+B67/H67</f>
+        <v>2.0000000677184064</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>70</v>
+      </c>
+      <c r="B69">
+        <v>0.45415154287117893</v>
+      </c>
+      <c r="D69">
+        <f>1-B69</f>
+        <v>0.54584845712882113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70">
+        <f>+J67</f>
+        <v>2.0000000677184064</v>
+      </c>
+      <c r="F70">
+        <f>+B70*B69*(B66^D69)*(B65^(B69-1))</f>
+        <v>1.1108938143082672</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="F71">
+        <f>+D69*B70*(B66^(D69-1))*(B65^B69)</f>
+        <v>0.92331451917543572</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75">
+        <v>8.7999999999999995E-2</v>
+      </c>
+      <c r="D75">
+        <f>7.5+8.8+56</f>
+        <v>72.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B20">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B43:B45">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:B55">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18:M18">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:N14">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="notEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
   <dimension ref="A1:Y58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -5157,7 +7072,7 @@
         <v>16.179579813090001</v>
       </c>
       <c r="X2" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.15">
@@ -5232,7 +7147,7 @@
         <v>18.697038467719992</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.15">
@@ -5311,9 +7226,9 @@
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
       <c r="E5" s="5">
         <v>0</v>
       </c>
@@ -5363,7 +7278,7 @@
       <c r="U5" s="5">
         <v>0.16482158305</v>
       </c>
-      <c r="V5" s="11"/>
+      <c r="V5" s="9"/>
       <c r="W5" s="5">
         <f t="shared" si="0"/>
         <v>14.60937084733</v>
@@ -5377,9 +7292,9 @@
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
       <c r="E6" s="5">
         <v>0</v>
       </c>
@@ -5429,7 +7344,7 @@
       <c r="U6" s="5">
         <v>20.612622200999997</v>
       </c>
-      <c r="V6" s="11"/>
+      <c r="V6" s="9"/>
       <c r="W6" s="5">
         <f t="shared" si="0"/>
         <v>24.824325021429996</v>
@@ -5443,9 +7358,9 @@
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
       <c r="E7" s="5">
         <v>0</v>
       </c>
@@ -5495,7 +7410,7 @@
       <c r="U7" s="5">
         <v>3.5847821083199998</v>
       </c>
-      <c r="V7" s="11"/>
+      <c r="V7" s="9"/>
       <c r="W7" s="5">
         <f t="shared" si="0"/>
         <v>51.445617916001666</v>
@@ -5837,12 +7752,12 @@
       <c r="O12" s="5">
         <v>5.8828657</v>
       </c>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
       <c r="R12" s="5">
         <v>7.3869768860000002</v>
       </c>
-      <c r="S12" s="11"/>
+      <c r="S12" s="9"/>
       <c r="T12" s="5">
         <v>0</v>
       </c>
@@ -6073,13 +7988,13 @@
         <v>5.8828657</v>
       </c>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.15">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
       <c r="E16" s="5">
         <v>0</v>
       </c>
@@ -6139,14 +8054,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="5">
         <v>0</v>
       </c>
-      <c r="C17" s="11"/>
+      <c r="C17" s="9"/>
       <c r="D17" s="5">
         <v>0</v>
       </c>
@@ -6284,7 +8199,7 @@
         <v>7.3869768858900002</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -6297,9 +8212,9 @@
       <c r="D19" s="5">
         <v>0</v>
       </c>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="5">
         <v>0</v>
       </c>
@@ -6350,7 +8265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -6363,11 +8278,11 @@
       <c r="D20" s="5">
         <v>0</v>
       </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
       <c r="J20" s="5">
         <v>0</v>
       </c>
@@ -6470,7 +8385,7 @@
       <c r="S21" s="5">
         <v>0</v>
       </c>
-      <c r="T21" s="11"/>
+      <c r="T21" s="9"/>
       <c r="U21" s="5">
         <v>0</v>
       </c>
@@ -6482,7 +8397,7 @@
         <v>24.362225894000002</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -6543,7 +8458,7 @@
       <c r="T22" s="5">
         <v>0</v>
       </c>
-      <c r="U22" s="11"/>
+      <c r="U22" s="9"/>
       <c r="V22" s="5">
         <v>0</v>
       </c>
@@ -6815,8 +8730,8 @@
       <c r="J30" s="7"/>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>178</v>
+      <c r="A31" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7"/>
@@ -6845,52 +8760,52 @@
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B36" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B37" t="s">
-        <v>181</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B38" t="s">
-        <v>182</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
-        <v>183</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B42" t="s">
-        <v>185</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B44" t="s">
-        <v>186</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B45" t="s">
-        <v>187</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B46" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B48" t="s">
-        <v>189</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.15">
@@ -7002,7 +8917,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B58" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -7031,8 +8946,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
   <dimension ref="A1:AA39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
@@ -7182,7 +9100,7 @@
         <v>30.801579823690002</v>
       </c>
       <c r="X2" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.15">
@@ -7258,7 +9176,7 @@
         <v>64.195393330520005</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.15">
@@ -8937,9 +10855,9 @@
         <v>0.15030203489964825</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.15">
-      <c r="A31" s="10" t="s">
-        <v>178</v>
+    <row r="31" spans="1:23" ht="22.5" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.15">
@@ -8949,7 +10867,7 @@
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B39" t="s">
-        <v>179</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -8973,9 +10891,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:AA55"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
@@ -9123,7 +11041,7 @@
         <v>30.814313510200002</v>
       </c>
       <c r="X2" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.15">
@@ -9198,7 +11116,7 @@
         <v>64.215721992000013</v>
       </c>
       <c r="X3" t="s">
-        <v>177</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.15">
@@ -10867,13 +12785,13 @@
         <v>89.312344979199992</v>
       </c>
       <c r="I29" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="J29" t="s">
-        <v>172</v>
+        <v>47</v>
       </c>
       <c r="K29" t="s">
-        <v>171</v>
+        <v>46</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>3</v>
@@ -11039,13 +12957,13 @@
         <v>22</v>
       </c>
       <c r="I34" t="s">
-        <v>173</v>
+        <v>48</v>
       </c>
       <c r="J34" t="s">
-        <v>174</v>
+        <v>49</v>
       </c>
       <c r="K34" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>1</v>
@@ -11335,1046 +13253,6 @@
       <c r="D55">
         <f t="shared" si="17"/>
         <v>3.0023476153009872E-2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B58" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B59" t="s">
-        <v>46</v>
-      </c>
-      <c r="E59" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B60" t="s">
-        <v>47</v>
-      </c>
-      <c r="E60" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B61" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B62" t="s">
-        <v>49</v>
-      </c>
-      <c r="E62">
-        <f>+I10/I23</f>
-        <v>0.2228790814165896</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B63" t="s">
-        <v>50</v>
-      </c>
-      <c r="E63">
-        <f>+I11/I23</f>
-        <v>0.57465863931136241</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B64" t="s">
-        <v>51</v>
-      </c>
-      <c r="E64">
-        <f>+I20/I23</f>
-        <v>0.18433194114924564</v>
-      </c>
-    </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B65" t="s">
-        <v>52</v>
-      </c>
-      <c r="E65">
-        <f>+I12/I23</f>
-        <v>1.8130338122802327E-2</v>
-      </c>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B66" t="s">
-        <v>53</v>
-      </c>
-      <c r="E66">
-        <f>+J15/J23</f>
-        <v>1.6970928970380987E-2</v>
-      </c>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B67" t="s">
-        <v>54</v>
-      </c>
-      <c r="E67" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B68" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68">
-        <f>+J21/J23</f>
-        <v>7.5915120524246593E-2</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B69" t="s">
-        <v>56</v>
-      </c>
-      <c r="E69">
-        <f>+J13/J23</f>
-        <v>0.10501323967174463</v>
-      </c>
-    </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B70" t="s">
-        <v>57</v>
-      </c>
-      <c r="E70">
-        <f>+K10/J23</f>
-        <v>0.24469244356124703</v>
-      </c>
-      <c r="F70" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B71" t="s">
-        <v>58</v>
-      </c>
-      <c r="E71">
-        <f>+L10/J23</f>
-        <v>2.9582435571151724E-2</v>
-      </c>
-      <c r="F71" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B72" t="s">
-        <v>59</v>
-      </c>
-      <c r="E72">
-        <f>+N10/J23</f>
-        <v>7.7301487022869847E-2</v>
-      </c>
-      <c r="F72" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B73" t="s">
-        <v>60</v>
-      </c>
-      <c r="E73">
-        <f>+K21/K23</f>
-        <v>0.36058999678606596</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B74" t="s">
-        <v>61</v>
-      </c>
-      <c r="E74">
-        <f>+M11/M23</f>
-        <v>0.78292960782039611</v>
-      </c>
-      <c r="F74" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E75">
-        <f>+K14/N23</f>
-        <v>0.27663994090528682</v>
-      </c>
-      <c r="F75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B76" t="s">
-        <v>62</v>
-      </c>
-      <c r="E76" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B77" t="s">
-        <v>158</v>
-      </c>
-      <c r="E77">
-        <f>+L14/N23</f>
-        <v>0.72336005909471324</v>
-      </c>
-      <c r="F77" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B78" t="s">
-        <v>63</v>
-      </c>
-      <c r="E78">
-        <f>+M12/M23</f>
-        <v>0.21707039217960386</v>
-      </c>
-      <c r="F78" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B79" t="s">
-        <v>64</v>
-      </c>
-      <c r="E79">
-        <f>+L21/L23</f>
-        <v>0.11979308595961004</v>
-      </c>
-    </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B80" t="s">
-        <v>65</v>
-      </c>
-      <c r="E80" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B81" t="s">
-        <v>66</v>
-      </c>
-      <c r="E81" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B82" t="s">
-        <v>67</v>
-      </c>
-      <c r="E82" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B83" t="s">
-        <v>68</v>
-      </c>
-      <c r="E83">
-        <f>+E19/E20</f>
-        <v>1.3782695325340365E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B84" t="s">
-        <v>69</v>
-      </c>
-      <c r="E84">
-        <f>+F19/F20</f>
-        <v>1.8358868621116162E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B85" t="s">
-        <v>70</v>
-      </c>
-      <c r="E85">
-        <f>+G19/G20</f>
-        <v>7.8594640160204336E-6</v>
-      </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B86" t="s">
-        <v>71</v>
-      </c>
-      <c r="E86" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B87" t="s">
-        <v>72</v>
-      </c>
-      <c r="E87" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B88" t="s">
-        <v>73</v>
-      </c>
-      <c r="E88" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B89" t="s">
-        <v>74</v>
-      </c>
-      <c r="E89" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B90" t="s">
-        <v>75</v>
-      </c>
-      <c r="E90" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B91" t="s">
-        <v>76</v>
-      </c>
-      <c r="E91" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B92" t="s">
-        <v>77</v>
-      </c>
-      <c r="E92" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B93" t="s">
-        <v>78</v>
-      </c>
-      <c r="E93" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B94" t="s">
-        <v>79</v>
-      </c>
-      <c r="E94" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B95" t="s">
-        <v>80</v>
-      </c>
-      <c r="E95" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B96" t="s">
-        <v>81</v>
-      </c>
-      <c r="E96" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="97" spans="2:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B97" t="s">
-        <v>82</v>
-      </c>
-      <c r="E97" t="s">
-        <v>154</v>
-      </c>
-      <c r="H97" s="9"/>
-    </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B98" t="s">
-        <v>83</v>
-      </c>
-      <c r="E98" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B99" t="s">
-        <v>84</v>
-      </c>
-      <c r="E99" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B100" t="s">
-        <v>85</v>
-      </c>
-      <c r="E100" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B101" t="s">
-        <v>86</v>
-      </c>
-      <c r="E101" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B102" t="s">
-        <v>87</v>
-      </c>
-      <c r="E102" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B103" t="s">
-        <v>88</v>
-      </c>
-      <c r="E103" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B104" t="s">
-        <v>89</v>
-      </c>
-      <c r="E104" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B105" t="s">
-        <v>90</v>
-      </c>
-      <c r="E105" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B106" t="s">
-        <v>91</v>
-      </c>
-      <c r="E106" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B107" t="s">
-        <v>92</v>
-      </c>
-      <c r="E107" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B108" t="s">
-        <v>93</v>
-      </c>
-      <c r="E108" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B109" t="s">
-        <v>94</v>
-      </c>
-      <c r="E109" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B110" t="s">
-        <v>95</v>
-      </c>
-      <c r="E110" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B111" t="s">
-        <v>96</v>
-      </c>
-      <c r="E111" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.15">
-      <c r="B112" t="s">
-        <v>97</v>
-      </c>
-      <c r="E112" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B113" t="s">
-        <v>98</v>
-      </c>
-      <c r="E113" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B114" t="s">
-        <v>99</v>
-      </c>
-      <c r="E114" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B115" t="s">
-        <v>100</v>
-      </c>
-      <c r="E115" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B116" t="s">
-        <v>101</v>
-      </c>
-      <c r="E116" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B117" t="s">
-        <v>102</v>
-      </c>
-      <c r="E117" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B118" t="s">
-        <v>103</v>
-      </c>
-      <c r="E118" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B119" t="s">
-        <v>104</v>
-      </c>
-      <c r="E119" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B120" t="s">
-        <v>105</v>
-      </c>
-      <c r="E120" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B121" t="s">
-        <v>106</v>
-      </c>
-      <c r="E121" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B122" t="s">
-        <v>107</v>
-      </c>
-      <c r="E122" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B123" t="s">
-        <v>108</v>
-      </c>
-      <c r="E123" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B124" t="s">
-        <v>109</v>
-      </c>
-      <c r="E124" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B125" t="s">
-        <v>110</v>
-      </c>
-      <c r="E125" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B126" t="s">
-        <v>111</v>
-      </c>
-      <c r="E126" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B127" t="s">
-        <v>112</v>
-      </c>
-      <c r="E127" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B128" t="s">
-        <v>113</v>
-      </c>
-      <c r="E128" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B129" t="s">
-        <v>114</v>
-      </c>
-      <c r="E129" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B130" t="s">
-        <v>115</v>
-      </c>
-      <c r="E130" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B131" t="s">
-        <v>116</v>
-      </c>
-      <c r="E131" s="7">
-        <f>+J6</f>
-        <v>23.08991091</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B132" t="s">
-        <v>117</v>
-      </c>
-      <c r="E132" s="7">
-        <f>+J7</f>
-        <v>32.838168070000002</v>
-      </c>
-    </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B133" t="s">
-        <v>161</v>
-      </c>
-      <c r="E133" s="8">
-        <f>+E2</f>
-        <v>28.80303928</v>
-      </c>
-    </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B134" t="s">
-        <v>162</v>
-      </c>
-      <c r="E134" s="7">
-        <f>+F2</f>
-        <v>1.069724034</v>
-      </c>
-    </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B135" t="s">
-        <v>163</v>
-      </c>
-      <c r="E135" s="7">
-        <f>+G2</f>
-        <v>0.94155019620000002</v>
-      </c>
-    </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B136" t="s">
-        <v>164</v>
-      </c>
-      <c r="E136" s="7">
-        <f>+E3</f>
-        <v>0.17356569899999999</v>
-      </c>
-    </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B137" t="s">
-        <v>165</v>
-      </c>
-      <c r="E137" s="7">
-        <f>+F3</f>
-        <v>62.723730200000006</v>
-      </c>
-    </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B138" t="s">
-        <v>166</v>
-      </c>
-      <c r="E138" s="7">
-        <f>+G4</f>
-        <v>87.052368689999994</v>
-      </c>
-    </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B139" t="s">
-        <v>167</v>
-      </c>
-      <c r="E139" s="7">
-        <f>+E4</f>
-        <v>0</v>
-      </c>
-      <c r="J139" s="7"/>
-    </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B140" t="s">
-        <v>168</v>
-      </c>
-      <c r="E140" s="7">
-        <f>+F4</f>
-        <v>1.495441644</v>
-      </c>
-      <c r="J140" s="7"/>
-    </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B141" t="s">
-        <v>169</v>
-      </c>
-      <c r="E141" s="7">
-        <f>+G4</f>
-        <v>87.052368689999994</v>
-      </c>
-      <c r="G141" s="7"/>
-      <c r="J141" s="7"/>
-    </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B142" t="s">
-        <v>118</v>
-      </c>
-      <c r="E142" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B143" t="s">
-        <v>119</v>
-      </c>
-      <c r="E143" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.15">
-      <c r="B144" t="s">
-        <v>120</v>
-      </c>
-      <c r="E144" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B145" t="s">
-        <v>121</v>
-      </c>
-      <c r="E145" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B146" t="s">
-        <v>122</v>
-      </c>
-      <c r="E146" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B147" t="s">
-        <v>123</v>
-      </c>
-      <c r="E147" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B148" t="s">
-        <v>124</v>
-      </c>
-      <c r="E148" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B149" t="s">
-        <v>125</v>
-      </c>
-      <c r="E149" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B150" t="s">
-        <v>126</v>
-      </c>
-      <c r="E150" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B151" t="s">
-        <v>127</v>
-      </c>
-      <c r="E151" s="7">
-        <f>+B8</f>
-        <v>2.9878268870000002</v>
-      </c>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B152" t="s">
-        <v>128</v>
-      </c>
-      <c r="E152" s="7">
-        <f>+C8</f>
-        <v>7.1010807900000001</v>
-      </c>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B153" t="s">
-        <v>129</v>
-      </c>
-      <c r="E153" s="7">
-        <f>+D8</f>
-        <v>24.0441237</v>
-      </c>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B154" t="s">
-        <v>130</v>
-      </c>
-      <c r="E154">
-        <f>+E20/(E23-E18-E19)</f>
-        <v>0.1653833015987631</v>
-      </c>
-    </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B155" t="s">
-        <v>131</v>
-      </c>
-      <c r="E155">
-        <f>+F20/(F23-F18-F19)</f>
-        <v>0.29168195315061557</v>
-      </c>
-    </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B156" t="s">
-        <v>132</v>
-      </c>
-      <c r="E156">
-        <f>+G20/(G23-G18-G19)</f>
-        <v>4.7714219115788353E-2</v>
-      </c>
-    </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B157" t="s">
-        <v>133</v>
-      </c>
-      <c r="E157">
-        <f>+T5/W5</f>
-        <v>0.5250945791341679</v>
-      </c>
-    </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B158" t="s">
-        <v>134</v>
-      </c>
-      <c r="E158">
-        <f t="shared" ref="E158:E159" si="18">+T6/W6</f>
-        <v>0.13807183244507004</v>
-      </c>
-    </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B159" t="s">
-        <v>135</v>
-      </c>
-      <c r="E159">
-        <f t="shared" si="18"/>
-        <v>7.4788376503137119E-2</v>
-      </c>
-    </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B160" t="s">
-        <v>136</v>
-      </c>
-      <c r="E160">
-        <f>+L5/W5</f>
-        <v>5.0019380548486318E-4</v>
-      </c>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B161" t="s">
-        <v>137</v>
-      </c>
-      <c r="E161">
-        <f t="shared" ref="E161:E162" si="19">+L6/W6</f>
-        <v>8.568947282965333E-4</v>
-      </c>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B162" t="s">
-        <v>138</v>
-      </c>
-      <c r="E162">
-        <f t="shared" si="19"/>
-        <v>0.11014684436832699</v>
-      </c>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B163" t="s">
-        <v>139</v>
-      </c>
-      <c r="E163">
-        <f>+SUM(B16:B18)/B23</f>
-        <v>3.7232768160635663E-3</v>
-      </c>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B164" t="s">
-        <v>140</v>
-      </c>
-      <c r="E164">
-        <f>+SUM(C16:C18)/C23</f>
-        <v>1.8997600219906683E-2</v>
-      </c>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B165" t="s">
-        <v>141</v>
-      </c>
-      <c r="E165">
-        <f>+SUM(D16:D18)/D23</f>
-        <v>2.914834161367201E-2</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B166" t="s">
-        <v>142</v>
-      </c>
-      <c r="E166">
-        <f>+E18/(E23-E18)</f>
-        <v>7.3213641014702319E-3</v>
-      </c>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B167" t="s">
-        <v>143</v>
-      </c>
-      <c r="E167">
-        <f>+F18/(F23-F18)</f>
-        <v>5.4320547480447838E-2</v>
-      </c>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B168" t="s">
-        <v>144</v>
-      </c>
-      <c r="E168">
-        <f>+G18/(G23-G18)</f>
-        <v>6.1691197133121227E-3</v>
-      </c>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B169" t="s">
-        <v>145</v>
-      </c>
-      <c r="E169" s="7">
-        <f>+B5</f>
-        <v>3.1605375580000001</v>
-      </c>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B170" t="s">
-        <v>146</v>
-      </c>
-      <c r="E170" s="7">
-        <f>+C5</f>
-        <v>11.927984220000001</v>
-      </c>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B171" t="s">
-        <v>147</v>
-      </c>
-      <c r="E171" s="7">
-        <f>+D5</f>
-        <v>0.16408898730000002</v>
-      </c>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B172" t="s">
-        <v>148</v>
-      </c>
-      <c r="E172" s="7">
-        <f>+B6</f>
-        <v>6.9137747879999996</v>
-      </c>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B173" t="s">
-        <v>149</v>
-      </c>
-      <c r="E173" s="7">
-        <f>+C6</f>
-        <v>22.11542081</v>
-      </c>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B174" t="s">
-        <v>150</v>
-      </c>
-      <c r="E174" s="7">
-        <f>+D6</f>
-        <v>11.39658985</v>
-      </c>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B175" t="s">
-        <v>151</v>
-      </c>
-      <c r="E175" s="7">
-        <f>+B7</f>
-        <v>4.4456911320000003</v>
-      </c>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B176" t="s">
-        <v>152</v>
-      </c>
-      <c r="E176" s="7">
-        <f>+C7</f>
-        <v>10.25533388</v>
-      </c>
-    </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.15">
-      <c r="B177" t="s">
-        <v>153</v>
-      </c>
-      <c r="E177" s="7">
-        <f>+D7</f>
-        <v>25.790391530000001</v>
       </c>
     </row>
   </sheetData>
